--- a/docx/Báo cáo/Test case kiểm thử chức năng.xlsx
+++ b/docx/Báo cáo/Test case kiểm thử chức năng.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DoAnTotNghiep_NguyenQuyen_10122312\docx\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DoAnTotNghiep_NguyenQuyen_10122312\docx\Báo cáo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{159DF095-C80B-413C-B9DE-F14ABA13DE48}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69CB1A5C-CCB8-4156-B1FF-931F3E9D334E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9190" tabRatio="455" firstSheet="2" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9190" tabRatio="455" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TC_DangNhap" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="464" uniqueCount="169">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="464" uniqueCount="170">
   <si>
     <t>To Buglist</t>
   </si>
@@ -247,42 +247,10 @@
 Thông báo lỗi "Vui lòng điền vào trường này"</t>
   </si>
   <si>
-    <t xml:space="preserve">B1: Truy cập vào website https://debac.vn/
-B2: Chọn chức năng đăng ký
-B3: Nhập email: 
-B4: Nhập mật khẩu: ngminhtu
-B5: Nhập xác nhânh mật khẩu: ngminhtu
-B6: Nhấn "Đăng ký" </t>
-  </si>
-  <si>
-    <t xml:space="preserve">B1: Truy cập vào website https://debac.vn/
-B2: Chọn chức năng đăng ký
-B3: Nhập email: ngminhtu@gmail.com
-B4: Nhập mật khẩu: 
-B5: Nhập xác nhânh mật khẩu: ngminhtu
-B6: Nhấn "Đăng ký" </t>
-  </si>
-  <si>
-    <t xml:space="preserve">B1: Truy cập vào website https://debac.vn/
-B2: Chọn chức năng đăng ký
-B3: Nhập email: ngminhtu@gmail.com
-B4: Nhập mật khẩu: ngminhtu
-B5: Nhập xác nhânh mật khẩu: 
-B6: Nhấn "Đăng ký" </t>
-  </si>
-  <si>
     <t>bỏ trống xác nhận mật khẩu</t>
   </si>
   <si>
     <t>email thiếu @</t>
-  </si>
-  <si>
-    <t xml:space="preserve">B1: Truy cập vào website https://debac.vn/
-B2: Chọn chức năng đăng ký
-B3: Nhập email: ngminhtu.com
-B4: Nhập mật khẩu: ngminhtu
-B5: Nhập xác nhânh mật khẩu: ngminhtu
-B6: Nhấn "Đăng ký" </t>
   </si>
   <si>
     <t>Hiển thị trang chủ Ella
@@ -293,23 +261,7 @@
     <t>email thiếu sau @</t>
   </si>
   <si>
-    <t xml:space="preserve">B1: Truy cập vào website https://debac.vn/
-B2: Chọn chức năng đăng ký
-B3: Nhập email: ngminhtu@
-B4: Nhập mật khẩu: ngminhtu
-B5: Nhập xác nhânh mật khẩu: ngminhtu
-B6: Nhấn "Đăng ký" </t>
-  </si>
-  <si>
     <t>Mật khẩu &lt; 6 ký tự</t>
-  </si>
-  <si>
-    <t xml:space="preserve">B1: Truy cập vào website https://debac.vn/
-B2: Chọn chức năng đăng ký
-B3: Nhập email: ngminhtu@gmail.com
-B4: Nhập mật khẩu: ngmi
-B5: Nhập xác nhânh mật khẩu: ngmi
-B6: Nhấn "Đăng ký" </t>
   </si>
   <si>
     <t>Hiển thị trang chủ Ella
@@ -537,31 +489,7 @@
     <t>email thiếu trước @</t>
   </si>
   <si>
-    <t xml:space="preserve">B1: Truy cập vào website https://debac.vn/
-B2: Chọn chức năng đăng ký
-B3: Nhập email: @gmail.com
-B4: Nhập mật khẩu: ngminhtu
-B5: Nhập xác nhânh mật khẩu: ngminhtu
-B6: Nhấn "Đăng ký" </t>
-  </si>
-  <si>
-    <t xml:space="preserve">B1: Truy cập vào website https://debac.vn/
-B2: Chọn chức năng đăng ký
-B3: Nhập email: hoanganh@gmail.com
-B4: Nhập mật khẩu: hoanganh
-B5: Nhập xác nhânh mật khẩu: hoanganh1
-B6: Nhấn "Đăng ký" </t>
-  </si>
-  <si>
     <t>vị trí dấu '.' sai</t>
-  </si>
-  <si>
-    <t xml:space="preserve">B1: Truy cập vào website https://debac.vn/
-B2: Chọn chức năng đăng ký
-B3: Nhập email: ngminhtu@gmail.
-B4: Nhập mật khẩu: ngminhtu
-B5: Nhập xác nhânh mật khẩu: ngminhtu
-B6: Nhấn "Đăng ký" </t>
   </si>
   <si>
     <t>Hiển thị trang chủ Ella
@@ -970,6 +898,81 @@
   <si>
     <t>Đăng nhập thành công
 Hệ thống thông báo "Vui lòng nhập ít nhất một số điện thoại bạn đang sử dụng"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B1: Truy cập vào website https://ella.vn/
+B2: Chọn chức năng đăng ký
+B3: Nhập email: ngminhtu@gmail.com
+B4: Nhập mật khẩu: ngmi
+B5: Nhập xác nhânh mật khẩu: ngmi
+B6: Nhấn "Đăng ký" </t>
+  </si>
+  <si>
+    <t xml:space="preserve">B1: Truy cập vào website https://ella.vn/
+B2: Chọn chức năng đăng ký
+B3: Nhập email: hoanganh@gmail.com
+B4: Nhập mật khẩu: hoanganh
+B5: Nhập xác nhânh mật khẩu: hoanganh1
+B6: Nhấn "Đăng ký" </t>
+  </si>
+  <si>
+    <t xml:space="preserve">B1: Truy cập vào website https://ella.vn/
+B2: Chọn chức năng đăng ký
+B3: Nhập email: 
+B4: Nhập mật khẩu: ngminhtu
+B5: Nhập xác nhânh mật khẩu: ngminhtu
+B6: Nhấn "Đăng ký" </t>
+  </si>
+  <si>
+    <t xml:space="preserve">B1: Truy cập vào website https://ella.vn/
+B2: Chọn chức năng đăng ký
+B3: Nhập email: ngminhtu@gmail.com
+B4: Nhập mật khẩu: 
+B5: Nhập xác nhânh mật khẩu: ngminhtu
+B6: Nhấn "Đăng ký" </t>
+  </si>
+  <si>
+    <t xml:space="preserve">B1: Truy cập vào website https://ella.vn/
+B2: Chọn chức năng đăng ký
+B3: Nhập email: ngminhtu@gmail.com
+B4: Nhập mật khẩu: ngminhtu
+B5: Nhập xác nhânh mật khẩu: 
+B6: Nhấn "Đăng ký" </t>
+  </si>
+  <si>
+    <t xml:space="preserve">B1: Truy cập vào website https://ella.vn/
+B2: Chọn chức năng đăng ký
+B3: Nhập email: ngminhtu.com
+B4: Nhập mật khẩu: ngminhtu
+B5: Nhập xác nhânh mật khẩu: ngminhtu
+B6: Nhấn "Đăng ký" </t>
+  </si>
+  <si>
+    <t xml:space="preserve">B1: Truy cập vào website https://ella.vn/
+B2: Chọn chức năng đăng ký
+B3: Nhập email: ngminhtu@
+B4: Nhập mật khẩu: ngminhtu
+B5: Nhập xác nhânh mật khẩu: ngminhtu
+B6: Nhấn "Đăng ký" </t>
+  </si>
+  <si>
+    <t xml:space="preserve">B1: Truy cập vào website https://ella.vn/
+B2: Chọn chức năng đăng ký
+B3: Nhập email: @gmail.com
+B4: Nhập mật khẩu: ngminhtu
+B5: Nhập xác nhânh mật khẩu: ngminhtu
+B6: Nhấn "Đăng ký" </t>
+  </si>
+  <si>
+    <t xml:space="preserve">B1: Truy cập vào website https://ella.vn/
+B2: Chọn chức năng đăng ký
+B3: Nhập email: ngminhtu@gmail.
+B4: Nhập mật khẩu: ngminhtu
+B5: Nhập xác nhânh mật khẩu: ngminhtu
+B6: Nhấn "Đăng ký" </t>
+  </si>
+  <si>
+    <t>Fail: 0</t>
   </si>
 </sst>
 </file>
@@ -2053,19 +2056,19 @@
         <v>[DangKy - 02]</v>
       </c>
       <c r="B6" s="25" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="C6" s="31" t="s">
         <v>8</v>
       </c>
       <c r="D6" s="19" t="s">
-        <v>63</v>
+        <v>160</v>
       </c>
       <c r="E6" s="19" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="F6" s="19" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="G6" s="19" t="s">
         <v>11</v>
@@ -2081,19 +2084,19 @@
         <v>[DangKy - 03]</v>
       </c>
       <c r="B7" s="19" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="C7" s="31" t="s">
         <v>8</v>
       </c>
       <c r="D7" s="19" t="s">
-        <v>104</v>
+        <v>161</v>
       </c>
       <c r="E7" s="19" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="F7" s="19" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="G7" s="35" t="s">
         <v>12</v>
@@ -2102,7 +2105,7 @@
         <v>20</v>
       </c>
       <c r="I7" s="38" t="s">
-        <v>109</v>
+        <v>100</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="60">
@@ -2117,7 +2120,7 @@
         <v>8</v>
       </c>
       <c r="D8" s="19" t="s">
-        <v>53</v>
+        <v>162</v>
       </c>
       <c r="E8" s="19" t="s">
         <v>52</v>
@@ -2145,7 +2148,7 @@
         <v>8</v>
       </c>
       <c r="D9" s="19" t="s">
-        <v>54</v>
+        <v>163</v>
       </c>
       <c r="E9" s="19" t="s">
         <v>52</v>
@@ -2167,13 +2170,13 @@
         <v>[DangKy - 07]</v>
       </c>
       <c r="B10" s="25" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="C10" s="31" t="s">
         <v>8</v>
       </c>
       <c r="D10" s="19" t="s">
-        <v>55</v>
+        <v>164</v>
       </c>
       <c r="E10" s="19" t="s">
         <v>52</v>
@@ -2195,19 +2198,19 @@
         <v>[DangKy - 06]</v>
       </c>
       <c r="B11" s="25" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C11" s="31" t="s">
         <v>8</v>
       </c>
       <c r="D11" s="19" t="s">
-        <v>58</v>
+        <v>165</v>
       </c>
       <c r="E11" s="19" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="F11" s="19" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G11" s="19" t="s">
         <v>11</v>
@@ -2223,19 +2226,19 @@
         <v>[DangKy - 08]</v>
       </c>
       <c r="B12" s="25" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="C12" s="31" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="19" t="s">
-        <v>61</v>
+        <v>166</v>
       </c>
       <c r="E12" s="19" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="F12" s="19" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G12" s="19" t="s">
         <v>11</v>
@@ -2251,19 +2254,19 @@
         <v>[DangKy - 09]</v>
       </c>
       <c r="B13" s="19" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="C13" s="31" t="s">
         <v>8</v>
       </c>
       <c r="D13" s="19" t="s">
-        <v>103</v>
+        <v>167</v>
       </c>
       <c r="E13" s="19" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="F13" s="19" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G13" s="19" t="s">
         <v>11</v>
@@ -2279,19 +2282,19 @@
         <v>[DangKy - 10]</v>
       </c>
       <c r="B14" s="19" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="C14" s="31" t="s">
         <v>8</v>
       </c>
       <c r="D14" s="19" t="s">
-        <v>106</v>
+        <v>168</v>
       </c>
       <c r="E14" s="19" t="s">
-        <v>107</v>
+        <v>98</v>
       </c>
       <c r="F14" s="19" t="s">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="G14" s="19" t="s">
         <v>11</v>
@@ -2395,7 +2398,7 @@
         <v>15</v>
       </c>
       <c r="D4" s="23" t="s">
-        <v>16</v>
+        <v>169</v>
       </c>
       <c r="E4" s="23" t="s">
         <v>17</v>
@@ -2425,13 +2428,13 @@
         <v>9</v>
       </c>
       <c r="D5" s="19" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="E5" s="19" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="F5" s="19" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="G5" s="19" t="s">
         <v>11</v>
@@ -2446,19 +2449,19 @@
         <v>[TimKiemSP - 02]</v>
       </c>
       <c r="B6" s="28" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="C6" s="31" t="s">
         <v>9</v>
       </c>
       <c r="D6" s="19" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="E6" s="19" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="F6" s="19" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="G6" s="19" t="s">
         <v>11</v>
@@ -2473,19 +2476,19 @@
         <v>[TimKiemSP - 03]</v>
       </c>
       <c r="B7" s="28" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="C7" s="31" t="s">
         <v>9</v>
       </c>
       <c r="D7" s="19" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="E7" s="19" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="F7" s="19" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="G7" s="19" t="s">
         <v>11</v>
@@ -2507,13 +2510,13 @@
         <v>9</v>
       </c>
       <c r="D8" s="19" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="E8" s="19" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="F8" s="19" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="G8" s="19" t="s">
         <v>11</v>
@@ -2529,19 +2532,19 @@
         <v>[TimKiemSP - 05]</v>
       </c>
       <c r="B9" s="28" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="C9" s="31" t="s">
         <v>9</v>
       </c>
       <c r="D9" s="19" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="E9" s="19" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="F9" s="19" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="G9" s="28" t="s">
         <v>11</v>
@@ -2557,19 +2560,19 @@
         <v>[TimKiemSP - 06]</v>
       </c>
       <c r="B10" s="28" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="C10" s="31" t="s">
         <v>9</v>
       </c>
       <c r="D10" s="19" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="E10" s="19" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="F10" s="19" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="G10" s="28" t="s">
         <v>11</v>
@@ -2620,10 +2623,10 @@
   <sheetData>
     <row r="4" spans="6:9" ht="14.5">
       <c r="F4" s="40" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="G4" s="40" t="s">
-        <v>156</v>
+        <v>147</v>
       </c>
       <c r="H4" s="40" t="s">
         <v>11</v>
@@ -2634,7 +2637,7 @@
     </row>
     <row r="5" spans="6:9" ht="14.5">
       <c r="F5" s="39" t="s">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="G5" s="41">
         <v>10</v>
@@ -2648,7 +2651,7 @@
     </row>
     <row r="6" spans="6:9" ht="14.5">
       <c r="F6" s="45" t="s">
-        <v>148</v>
+        <v>139</v>
       </c>
       <c r="G6" s="46">
         <v>5</v>
@@ -2662,7 +2665,7 @@
     </row>
     <row r="7" spans="6:9" ht="14.5">
       <c r="F7" s="39" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="G7" s="41">
         <v>6</v>
@@ -2676,7 +2679,7 @@
     </row>
     <row r="8" spans="6:9" ht="14.5">
       <c r="F8" s="45" t="s">
-        <v>150</v>
+        <v>141</v>
       </c>
       <c r="G8" s="46">
         <v>11</v>
@@ -2690,7 +2693,7 @@
     </row>
     <row r="9" spans="6:9" ht="14.5">
       <c r="F9" s="39" t="s">
-        <v>151</v>
+        <v>142</v>
       </c>
       <c r="G9" s="41">
         <v>11</v>
@@ -2704,7 +2707,7 @@
     </row>
     <row r="10" spans="6:9" ht="14.5">
       <c r="F10" s="45" t="s">
-        <v>152</v>
+        <v>143</v>
       </c>
       <c r="G10" s="46">
         <v>8</v>
@@ -2718,7 +2721,7 @@
     </row>
     <row r="11" spans="6:9" ht="14.5">
       <c r="F11" s="43" t="s">
-        <v>157</v>
+        <v>148</v>
       </c>
       <c r="G11" s="44">
         <f>SUM(G5:G10)</f>
@@ -2855,13 +2858,13 @@
         <v>10</v>
       </c>
       <c r="D5" s="19" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="E5" s="19" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="F5" s="19" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="G5" s="19" t="s">
         <v>11</v>
@@ -2877,19 +2880,19 @@
         <v>[ThanhToan - 02]</v>
       </c>
       <c r="B6" s="19" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="C6" s="31" t="s">
         <v>10</v>
       </c>
       <c r="D6" s="19" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="E6" s="19" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="F6" s="19" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="G6" s="19" t="s">
         <v>11</v>
@@ -2905,19 +2908,19 @@
         <v>[ThanhToan - 03]</v>
       </c>
       <c r="B7" s="19" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="C7" s="31" t="s">
         <v>10</v>
       </c>
       <c r="D7" s="19" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="E7" s="19" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="F7" s="19" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="G7" s="35" t="s">
         <v>12</v>
@@ -2926,7 +2929,7 @@
         <v>20</v>
       </c>
       <c r="I7" s="38" t="s">
-        <v>126</v>
+        <v>117</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="100">
@@ -2935,19 +2938,19 @@
         <v>[ThanhToan - 04]</v>
       </c>
       <c r="B8" s="19" t="s">
-        <v>111</v>
+        <v>102</v>
       </c>
       <c r="C8" s="31" t="s">
         <v>10</v>
       </c>
       <c r="D8" s="19" t="s">
-        <v>112</v>
+        <v>103</v>
       </c>
       <c r="E8" s="19" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="F8" s="19" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="G8" s="19" t="s">
         <v>11</v>
@@ -2963,19 +2966,19 @@
         <v>[ThanhToan - 05]</v>
       </c>
       <c r="B9" s="19" t="s">
-        <v>153</v>
+        <v>144</v>
       </c>
       <c r="C9" s="31" t="s">
         <v>10</v>
       </c>
       <c r="D9" s="19" t="s">
-        <v>155</v>
+        <v>146</v>
       </c>
       <c r="E9" s="19" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="F9" s="19" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="G9" s="19" t="s">
         <v>11</v>
@@ -2997,13 +3000,13 @@
         <v>10</v>
       </c>
       <c r="D10" s="19" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="E10" s="19" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="F10" s="19" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="G10" s="19" t="s">
         <v>11</v>
@@ -3025,13 +3028,13 @@
         <v>10</v>
       </c>
       <c r="D11" s="19" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="E11" s="19" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="F11" s="19" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="G11" s="19" t="s">
         <v>11</v>
@@ -3047,19 +3050,19 @@
         <v>[ThanhToan - 08]</v>
       </c>
       <c r="B12" s="19" t="s">
-        <v>113</v>
+        <v>104</v>
       </c>
       <c r="C12" s="31" t="s">
         <v>10</v>
       </c>
       <c r="D12" s="19" t="s">
-        <v>116</v>
+        <v>107</v>
       </c>
       <c r="E12" s="19" t="s">
-        <v>120</v>
+        <v>111</v>
       </c>
       <c r="F12" s="19" t="s">
-        <v>121</v>
+        <v>112</v>
       </c>
       <c r="G12" s="19" t="s">
         <v>11</v>
@@ -3075,19 +3078,19 @@
         <v>[ThanhToan - 09]</v>
       </c>
       <c r="B13" s="19" t="s">
-        <v>114</v>
+        <v>105</v>
       </c>
       <c r="C13" s="31" t="s">
         <v>10</v>
       </c>
       <c r="D13" s="19" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="E13" s="19" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="F13" s="19" t="s">
-        <v>121</v>
+        <v>112</v>
       </c>
       <c r="G13" s="19" t="s">
         <v>11</v>
@@ -3103,19 +3106,19 @@
         <v>[ThanhToan - 10]</v>
       </c>
       <c r="B14" s="19" t="s">
-        <v>115</v>
+        <v>106</v>
       </c>
       <c r="C14" s="31" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="19" t="s">
-        <v>119</v>
+        <v>110</v>
       </c>
       <c r="E14" s="19" t="s">
-        <v>124</v>
+        <v>115</v>
       </c>
       <c r="F14" s="19" t="s">
-        <v>121</v>
+        <v>112</v>
       </c>
       <c r="G14" s="19" t="s">
         <v>11</v>
@@ -3131,19 +3134,19 @@
         <v>[ThanhToan - 11]</v>
       </c>
       <c r="B15" s="19" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="C15" s="31" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="19" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
       <c r="E15" s="19" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="F15" s="19" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="G15" s="19" t="s">
         <v>11</v>
@@ -3273,19 +3276,19 @@
         <v>[ChangeProfile - 01]</v>
       </c>
       <c r="B5" s="19" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="C5" s="31" t="s">
         <v>13</v>
       </c>
       <c r="D5" s="19" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="E5" s="19" t="s">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="F5" s="19" t="s">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="G5" s="19" t="s">
         <v>11</v>
@@ -3307,13 +3310,13 @@
         <v>13</v>
       </c>
       <c r="D6" s="19" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="E6" s="19" t="s">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="F6" s="19" t="s">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="G6" s="19" t="s">
         <v>11</v>
@@ -3335,13 +3338,13 @@
         <v>13</v>
       </c>
       <c r="D7" s="19" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="E7" s="19" t="s">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="F7" s="19" t="s">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="G7" s="19" t="s">
         <v>11</v>
@@ -3357,19 +3360,19 @@
         <v>[ChangeProfile - 04]</v>
       </c>
       <c r="B8" s="19" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="C8" s="31" t="s">
         <v>13</v>
       </c>
       <c r="D8" s="19" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="E8" s="19" t="s">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="F8" s="19" t="s">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="G8" s="19" t="s">
         <v>11</v>
@@ -3385,19 +3388,19 @@
         <v>[ChangeProfile - 05]</v>
       </c>
       <c r="B9" s="19" t="s">
-        <v>127</v>
+        <v>118</v>
       </c>
       <c r="C9" s="31" t="s">
         <v>13</v>
       </c>
       <c r="D9" s="19" t="s">
-        <v>128</v>
+        <v>119</v>
       </c>
       <c r="E9" s="19" t="s">
-        <v>168</v>
+        <v>159</v>
       </c>
       <c r="F9" s="19" t="s">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="G9" s="35" t="s">
         <v>12</v>
@@ -3406,7 +3409,7 @@
         <v>20</v>
       </c>
       <c r="I9" s="38" t="s">
-        <v>132</v>
+        <v>123</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="80">
@@ -3415,19 +3418,19 @@
         <v>[ChangeProfile - 06]</v>
       </c>
       <c r="B10" s="19" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="C10" s="31" t="s">
         <v>13</v>
       </c>
       <c r="D10" s="19" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="E10" s="19" t="s">
-        <v>168</v>
+        <v>159</v>
       </c>
       <c r="F10" s="19" t="s">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="G10" s="35" t="s">
         <v>12</v>
@@ -3436,7 +3439,7 @@
         <v>20</v>
       </c>
       <c r="I10" s="38" t="s">
-        <v>133</v>
+        <v>124</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="80">
@@ -3445,19 +3448,19 @@
         <v>[ChangeProfile - 07]</v>
       </c>
       <c r="B11" s="19" t="s">
-        <v>129</v>
+        <v>120</v>
       </c>
       <c r="C11" s="31" t="s">
         <v>13</v>
       </c>
       <c r="D11" s="19" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="E11" s="19" t="s">
-        <v>168</v>
+        <v>159</v>
       </c>
       <c r="F11" s="19" t="s">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="G11" s="35" t="s">
         <v>12</v>
@@ -3466,7 +3469,7 @@
         <v>20</v>
       </c>
       <c r="I11" s="38" t="s">
-        <v>134</v>
+        <v>125</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="80">
@@ -3475,19 +3478,19 @@
         <v>[ChangeProfile - 08]</v>
       </c>
       <c r="B12" s="19" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="C12" s="31" t="s">
         <v>13</v>
       </c>
       <c r="D12" s="19" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="E12" s="19" t="s">
-        <v>168</v>
+        <v>159</v>
       </c>
       <c r="F12" s="19" t="s">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="G12" s="35" t="s">
         <v>12</v>
@@ -3496,20 +3499,21 @@
         <v>20</v>
       </c>
       <c r="I12" s="38" t="s">
-        <v>135</v>
+        <v>126</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="B1" location="BugList!A1" display="To Buglist" xr:uid="{6F980733-6528-424B-B45A-75D8EB680571}"/>
     <hyperlink ref="A1" r:id="rId1" xr:uid="{79014417-D33A-48E5-ABCD-22679886FC3B}"/>
-    <hyperlink ref="I9" r:id="rId2" display="..\screenshots\E2E_login_20260517_213426_5_20260519_030532.png" xr:uid="{24F2C39C-A2BF-4E1D-BEC4-DB37E8FBD3D9}"/>
+    <hyperlink ref="I9" r:id="rId2" xr:uid="{24F2C39C-A2BF-4E1D-BEC4-DB37E8FBD3D9}"/>
     <hyperlink ref="I10" r:id="rId3" xr:uid="{E5BA72D2-91F9-470C-A182-B694505EAA04}"/>
     <hyperlink ref="I11" r:id="rId4" xr:uid="{AE3A4F13-1BDE-4CB0-852A-ED458A6944D6}"/>
     <hyperlink ref="I12" r:id="rId5" xr:uid="{B9092595-C182-4014-8309-32004122821E}"/>
     <hyperlink ref="I9:I12" r:id="rId6" display="E2E_login_20260517_213426_5_.png" xr:uid="{AA14C026-3BC7-4CAE-A88E-E9CEB146D70C}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId7"/>
 </worksheet>
 </file>
 
@@ -3628,13 +3632,13 @@
         <v>10</v>
       </c>
       <c r="D5" s="19" t="s">
-        <v>136</v>
+        <v>127</v>
       </c>
       <c r="E5" s="19" t="s">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="F5" s="19" t="s">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="G5" s="19" t="s">
         <v>11</v>
@@ -3650,19 +3654,19 @@
         <v>[ThanhToan - 02]</v>
       </c>
       <c r="B6" s="19" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="C6" s="31" t="s">
         <v>10</v>
       </c>
       <c r="D6" s="19" t="s">
-        <v>137</v>
+        <v>128</v>
       </c>
       <c r="E6" s="19" t="s">
-        <v>159</v>
+        <v>150</v>
       </c>
       <c r="F6" s="19" t="s">
-        <v>159</v>
+        <v>150</v>
       </c>
       <c r="G6" s="19" t="s">
         <v>11</v>
@@ -3678,19 +3682,19 @@
         <v>[ThanhToan - 03]</v>
       </c>
       <c r="B7" s="19" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="C7" s="31" t="s">
         <v>10</v>
       </c>
       <c r="D7" s="19" t="s">
-        <v>138</v>
+        <v>129</v>
       </c>
       <c r="E7" s="19" t="s">
-        <v>159</v>
+        <v>150</v>
       </c>
       <c r="F7" s="19" t="s">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="G7" s="35" t="s">
         <v>12</v>
@@ -3699,7 +3703,7 @@
         <v>20</v>
       </c>
       <c r="I7" s="38" t="s">
-        <v>126</v>
+        <v>117</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="120">
@@ -3708,19 +3712,19 @@
         <v>[ThanhToan - 04]</v>
       </c>
       <c r="B8" s="19" t="s">
-        <v>111</v>
+        <v>102</v>
       </c>
       <c r="C8" s="31" t="s">
         <v>10</v>
       </c>
       <c r="D8" s="19" t="s">
-        <v>139</v>
+        <v>130</v>
       </c>
       <c r="E8" s="19" t="s">
-        <v>159</v>
+        <v>150</v>
       </c>
       <c r="F8" s="19" t="s">
-        <v>159</v>
+        <v>150</v>
       </c>
       <c r="G8" s="19" t="s">
         <v>11</v>
@@ -3736,19 +3740,19 @@
         <v>[ThanhToan - 05]</v>
       </c>
       <c r="B9" s="19" t="s">
-        <v>153</v>
+        <v>144</v>
       </c>
       <c r="C9" s="31" t="s">
         <v>10</v>
       </c>
       <c r="D9" s="19" t="s">
-        <v>154</v>
+        <v>145</v>
       </c>
       <c r="E9" s="19" t="s">
-        <v>159</v>
+        <v>150</v>
       </c>
       <c r="F9" s="19" t="s">
-        <v>159</v>
+        <v>150</v>
       </c>
       <c r="G9" s="19" t="s">
         <v>11</v>
@@ -3770,13 +3774,13 @@
         <v>10</v>
       </c>
       <c r="D10" s="19" t="s">
-        <v>140</v>
+        <v>131</v>
       </c>
       <c r="E10" s="19" t="s">
-        <v>160</v>
+        <v>151</v>
       </c>
       <c r="F10" s="19" t="s">
-        <v>160</v>
+        <v>151</v>
       </c>
       <c r="G10" s="19" t="s">
         <v>11</v>
@@ -3798,13 +3802,13 @@
         <v>10</v>
       </c>
       <c r="D11" s="19" t="s">
-        <v>141</v>
+        <v>132</v>
       </c>
       <c r="E11" s="19" t="s">
-        <v>160</v>
+        <v>151</v>
       </c>
       <c r="F11" s="19" t="s">
-        <v>160</v>
+        <v>151</v>
       </c>
       <c r="G11" s="19" t="s">
         <v>11</v>
@@ -3820,19 +3824,19 @@
         <v>[ThanhToan - 07]</v>
       </c>
       <c r="B12" s="19" t="s">
-        <v>113</v>
+        <v>104</v>
       </c>
       <c r="C12" s="31" t="s">
         <v>10</v>
       </c>
       <c r="D12" s="19" t="s">
-        <v>142</v>
+        <v>133</v>
       </c>
       <c r="E12" s="19" t="s">
-        <v>161</v>
+        <v>152</v>
       </c>
       <c r="F12" s="19" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="G12" s="19" t="s">
         <v>11</v>
@@ -3848,19 +3852,19 @@
         <v>[ThanhToan - 08]</v>
       </c>
       <c r="B13" s="19" t="s">
-        <v>114</v>
+        <v>105</v>
       </c>
       <c r="C13" s="31" t="s">
         <v>10</v>
       </c>
       <c r="D13" s="19" t="s">
-        <v>143</v>
+        <v>134</v>
       </c>
       <c r="E13" s="19" t="s">
-        <v>162</v>
+        <v>153</v>
       </c>
       <c r="F13" s="19" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="G13" s="19" t="s">
         <v>11</v>
@@ -3876,19 +3880,19 @@
         <v>[ThanhToan - 10]</v>
       </c>
       <c r="B14" s="19" t="s">
-        <v>115</v>
+        <v>106</v>
       </c>
       <c r="C14" s="31" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="19" t="s">
-        <v>144</v>
+        <v>135</v>
       </c>
       <c r="E14" s="19" t="s">
-        <v>163</v>
+        <v>154</v>
       </c>
       <c r="F14" s="19" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="G14" s="19" t="s">
         <v>11</v>
@@ -3904,19 +3908,19 @@
         <v>[ThanhToan - 11]</v>
       </c>
       <c r="B15" s="19" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="C15" s="31" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="19" t="s">
-        <v>145</v>
+        <v>136</v>
       </c>
       <c r="E15" s="19" t="s">
-        <v>164</v>
+        <v>155</v>
       </c>
       <c r="F15" s="19" t="s">
-        <v>166</v>
+        <v>157</v>
       </c>
       <c r="G15" s="19" t="s">
         <v>11</v>

--- a/docx/Báo cáo/Test case kiểm thử chức năng.xlsx
+++ b/docx/Báo cáo/Test case kiểm thử chức năng.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DoAnTotNghiep_NguyenQuyen_10122312\docx\Báo cáo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69CB1A5C-CCB8-4156-B1FF-931F3E9D334E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00159B71-746D-444F-8169-052ACE5DF87E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9190" tabRatio="455" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9190" tabRatio="455" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TC_DangNhap" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="464" uniqueCount="170">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="464" uniqueCount="169">
   <si>
     <t>To Buglist</t>
   </si>
@@ -66,27 +66,15 @@
     <t>Nguyen Thi Quyen</t>
   </si>
   <si>
-    <t>Người dùng đã có tài khoản, chưa đăng nhập</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Người dùng chưa có tài khoản để đăng nhập vào hệ thống </t>
-  </si>
-  <si>
     <t>Người dùng đã truy cập vào trang web</t>
   </si>
   <si>
-    <t>Người dùng truy cập vào trang web</t>
-  </si>
-  <si>
     <t>Pass</t>
   </si>
   <si>
     <t>Fail</t>
   </si>
   <si>
-    <t>Người dùng đã đăng nhập vào trang web</t>
-  </si>
-  <si>
     <t xml:space="preserve">Test Case Description   </t>
   </si>
   <si>
@@ -121,12 +109,6 @@
   </si>
   <si>
     <t>Email, mật khẩu đúng</t>
-  </si>
-  <si>
-    <t>bỏ trống email</t>
-  </si>
-  <si>
-    <t>bỏ trống mật khẩu</t>
   </si>
   <si>
     <t>Test_Report</t>
@@ -167,812 +149,534 @@
     <t>ScreenShot</t>
   </si>
   <si>
-    <t>B1: Truy cập vào website https://ella.vn
-B2: Chọn chức năng đăng nhập
-B3: Nhập Email: tuyetmai99@gmail.com
-B4: Nhập password:
-B5: Nhấn "Đăng nhập"</t>
-  </si>
-  <si>
-    <t>B1: Truy cập vào website https://ella.vn
-B2: Chọn chức năng đăng nhập
-B3: Nhập Email: ngvanhoan@gmail.com
-B4: Nhập password: 123456789
-B5: Nhấn "Đăng nhập"</t>
-  </si>
-  <si>
-    <t>B1: Truy cập vào website https://ella.vn
-B2: Chọn chức năng đăng nhập
-B3: Nhập Email: ngvanhoan
-B4: Nhập password: ngvanhoan
-B5: Nhấn "Đăng nhập"</t>
-  </si>
-  <si>
-    <t>B1: Truy cập vào website https://ella.vn
-B2: Chọn chức năng đăng nhập
-B3: Bỏ trống Email
-B4: Nhập password: 123456789
-B5: Nhấn "Đăng nhập"</t>
-  </si>
-  <si>
-    <t>B1: Truy cập vào website https://ella.vn
-B2: Chọn chức năng đăng nhập
-B3: Nhập Email:ngvanhoan@gmail.com
-B4: Nhập password: ngvanhoan
-B5: Nhấn "Đăng nhập"</t>
-  </si>
-  <si>
     <t>Email đã sử dụng</t>
   </si>
   <si>
-    <t xml:space="preserve">B1: Truy cập vào website https://ella.vn/
-B2: Chọn chức năng đăng ký
-B3: Nhập email: ngminhtu@gmail.com
-B4: Nhập mật khẩu: ngminhtu
-B5: Nhập xác nhânh mật khẩu: ngminhtu
-B6: Nhấn "Đăng ký" </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hiển thị trang chủ Ella
-Hiển thị giao diện đăng nhập
-Thông báo lỗi và yêu cầu nhập lại. "Tài khoản hoặc mật khẩu không chính xác"
+    <t>Mật khẩu &lt; 6 ký tự</t>
+  </si>
+  <si>
+    <t>Tìm kiếm sản phẩm theo mã sản phẩm</t>
+  </si>
+  <si>
+    <t>Tìm kiếm sản phẩm với tên đầy đủ</t>
+  </si>
+  <si>
+    <t>Hệ thống hiện danh sách sản phẩm ngẫu nhiên</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bỏ trống </t>
+  </si>
+  <si>
+    <t>Hệ thống hiện thông báo "Vui lòng điền vào trường này"</t>
+  </si>
+  <si>
+    <t>Tìm kiếm với từ khóa không có trong sản phẩm</t>
+  </si>
+  <si>
+    <t>Hệ thống không hiện sản phẩm nào</t>
+  </si>
+  <si>
+    <t>Sai số điện thoại &lt;10 số</t>
+  </si>
+  <si>
+    <t>Sai số điện thoại &gt;10 số</t>
+  </si>
+  <si>
+    <t>Hệ thống thông báo "Đơn hàng của bạn đã được gửi đi"</t>
+  </si>
+  <si>
+    <t>Hệ thống thông báo "Vui lòng điền vào trường này"</t>
+  </si>
+  <si>
+    <t>Hệ thống thông báo "Vui lòng nhập ít nhất một số điện thoại bạn đang sử dụng"</t>
+  </si>
+  <si>
+    <t>cập nhật thành công</t>
+  </si>
+  <si>
+    <t>Bỏ trống địa chỉ</t>
+  </si>
+  <si>
+    <t>Số điện thoại &lt; 10 số</t>
+  </si>
+  <si>
+    <t>vị trí dấu '.' sai</t>
+  </si>
+  <si>
+    <t>register_Auto_Test_3_20260519_001508.png</t>
+  </si>
+  <si>
+    <t>Sai số điện thoại chứa ký tự đặc biệt</t>
+  </si>
+  <si>
+    <t>Email thiếu phần sau @</t>
+  </si>
+  <si>
+    <t>Email thiếu phần trước @</t>
+  </si>
+  <si>
+    <t>Email thiếu @</t>
+  </si>
+  <si>
+    <t>Hệ thống thông báo "Vui lòng nhập phần đứng sau @"</t>
+  </si>
+  <si>
+    <t>Hệ thống thông báo "Vui lòng"</t>
+  </si>
+  <si>
+    <t>Hệ thống thông báo "sai vị trí"</t>
+  </si>
+  <si>
+    <t>Hệ thống thông báo "Vui lòng nhập phần đứng trước @"</t>
+  </si>
+  <si>
+    <t>Hệ thống thông báo "Vui lòng nhập bao gồm '@' trong địa chỉ email"</t>
+  </si>
+  <si>
+    <t>Hệ thống thông báo "'.' bị sai vị trí trong '.'"</t>
+  </si>
+  <si>
+    <t>order_Auto_Test_3_20260515_165252.png</t>
+  </si>
+  <si>
+    <t>Số điện thoại chứa ký tự đặc biệt</t>
+  </si>
+  <si>
+    <t>Số điện thoại &gt; 10 số</t>
+  </si>
+  <si>
+    <t>Số điện thoại chứa chữ</t>
+  </si>
+  <si>
+    <t>E2E_login_20260517_213426_5_.png</t>
+  </si>
+  <si>
+    <t>E2E_login_20260517_213426_6.png</t>
+  </si>
+  <si>
+    <t>E2E_login_20260517_213426_7.png</t>
+  </si>
+  <si>
+    <t>E2E_login_20260517_213426_8.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chức năng </t>
+  </si>
+  <si>
+    <t>Đăng ký</t>
+  </si>
+  <si>
+    <t>Đăng nhập</t>
+  </si>
+  <si>
+    <t>Tìm kiếm</t>
+  </si>
+  <si>
+    <t>Đặt hàng</t>
+  </si>
+  <si>
+    <t>E2E Đặt hàng</t>
+  </si>
+  <si>
+    <t>Profile</t>
+  </si>
+  <si>
+    <t>Sai số điện thoại chứa chữ</t>
+  </si>
+  <si>
+    <t>Số lượng kịch bản</t>
+  </si>
+  <si>
+    <t>Tổng số</t>
+  </si>
+  <si>
+    <t>Người dùng đã có tài khoản, chưa đăng nhập và đang ở trang đăng nhập.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thông báo lỗi và yêu cầu nhập lại. "Tài khoản hoặc mật khẩu không chính xác"
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Hiển thị trang chủ Ella
-Hiển thị giao diện đăng nhập
-Thông báo lỗi và yêu cầu nhập lại. "Vui lòng điền vào trường này"
+    <t xml:space="preserve">Thông báo lỗi và yêu cầu nhập lại. "Vui lòng điền vào trường này"
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Hiển thị trang chủ Ella
-Hiển thị giao diện đăng nhập
-Chuyển hướng đến trang chủ
+    <t xml:space="preserve">Chuyển hướng đến trang chủ
 Cập nhật tên tài khoản </t>
   </si>
   <si>
-    <t>Hiển thị trang chủ Ella
-Hiển thị giao diện đăng nhập
-Chuyển hướng đến trang chủ
+    <t>Chuyển hướng đến trang chủ
 Cập nhật "Tài khoản"</t>
   </si>
   <si>
-    <t>Hiển thị trang chủ Ella
-Hiển thị giao diện đăng ký
-Thông báo lỗi "Email đã được sử dụng"</t>
-  </si>
-  <si>
-    <t>Hiển thị trang chủ Ella
-Hiển thị giao diện đăng ký
-Thông báo lỗi "Vui lòng điền vào trường này"</t>
-  </si>
-  <si>
-    <t>bỏ trống xác nhận mật khẩu</t>
-  </si>
-  <si>
-    <t>email thiếu @</t>
-  </si>
-  <si>
-    <t>Hiển thị trang chủ Ella
-Hiển thị giao diện đăng ký
-Thông báo "Vui lòng"</t>
-  </si>
-  <si>
-    <t>email thiếu sau @</t>
-  </si>
-  <si>
-    <t>Mật khẩu &lt; 6 ký tự</t>
-  </si>
-  <si>
-    <t>Hiển thị trang chủ Ella
-Hiển thị giao diện đăng ký
-Thông báo lỗi "Mật khẩu tối thiểu phải có 6 ký tự"</t>
-  </si>
-  <si>
-    <t>xác nhận mật khẩu không khớp với mật khẩu</t>
-  </si>
-  <si>
-    <t>Hiển thị trang chủ Ella
-Hiển thị giao diện đăng ký
-Thông báo lỗi "Xác nhận mật khẩu không khớp với mật khẩu"</t>
-  </si>
-  <si>
-    <t>Hiển thị trang chủ Ella
-Hiển thị giao diện đăng ký
-Đăng ký thành công</t>
-  </si>
-  <si>
-    <t xml:space="preserve">B1: Truy cập vào website https://ella.vn/
-B2: Click vào thanh tìm kiếm
-B3: Nhập: cao gót 7cm
-B4: Nhấn Enter hoặc biểu tượng tìm kiếm
+    <t>Xác nhận mật khẩu không khớp với mật khẩu</t>
+  </si>
+  <si>
+    <t>Bỏ trống xác nhận mật khẩu</t>
+  </si>
+  <si>
+    <t>Email thiếu sau @</t>
+  </si>
+  <si>
+    <t>Email thiếu trước @</t>
+  </si>
+  <si>
+    <t>Vị trí dấu '.' sai</t>
+  </si>
+  <si>
+    <t>Người dùng chưa có tài khoản để đăng nhập vào hệ thống, đang ở trang đăng ký</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B1: Nhập email đã đăng ký trước
+B2: Nhập mật khẩu và xác nhận mật khẩu
+B3: Nhấn "Đăng ký" </t>
+  </si>
+  <si>
+    <t xml:space="preserve">B1: Nhập email, xác nhận mật khẩu hợp lệ
+B2: Nhập mật khẩu &lt;6 kí tự
+B3: Nhấn "Đăng ký" </t>
+  </si>
+  <si>
+    <t xml:space="preserve">B1: Nhập email, mật khẩu
+B2: Nhập xác nhận mật khẩu khác mật khẩu
+B3: Nhấn "Đăng ký" </t>
+  </si>
+  <si>
+    <t xml:space="preserve">B1: Bỏ trống email
+B2: Nhập mật khẩu, xác nhận mật khẩu hợp lệ
+B3: Nhấn "Đăng ký" </t>
+  </si>
+  <si>
+    <t xml:space="preserve">B1: Nhập email, xác nhận mật khẩu
+B2: Bỏ trống mật khẩu
+B3: Nhấn "Đăng ký" </t>
+  </si>
+  <si>
+    <t xml:space="preserve">B1: Nhập email, mật khẩu
+B2: Bỏ trống xác nhận mật khẩu
+B3: Nhấn "Đăng ký" </t>
+  </si>
+  <si>
+    <t xml:space="preserve">B1: Nhập email thiếu @
+B2: Nhập mật khẩu và xác nhận mật khẩu
+B3: Nhấn "Đăng ký" </t>
+  </si>
+  <si>
+    <t xml:space="preserve">B1: Nhập email thiếu sau @
+B2: Nhập mật khẩu và xác nhận mật khẩu
+B3: Nhấn "Đăng ký" </t>
+  </si>
+  <si>
+    <t xml:space="preserve">B1: Nhập email thiếu trước @
+B2: Nhập mật khẩu và xác nhận mật khẩu
+B3: Nhấn "Đăng ký" </t>
+  </si>
+  <si>
+    <t xml:space="preserve">B1: Nhập email sai vị trí dấu '.'
+B2: Nhập mật khẩu và xác nhận mật khẩu
+B3: Nhấn "Đăng ký" </t>
+  </si>
+  <si>
+    <t>Thông báo lỗi "Email đã được sử dụng"</t>
+  </si>
+  <si>
+    <t>Thông báo lỗi "Mật khẩu tối thiểu phải có 6 ký tự"</t>
+  </si>
+  <si>
+    <t>Thông báo lỗi "Xác nhận mật khẩu không khớp với mật khẩu"</t>
+  </si>
+  <si>
+    <t>Thông báo lỗi "Vui lòng điền vào trường này"</t>
+  </si>
+  <si>
+    <t>Thông báo "Vui lòng"</t>
+  </si>
+  <si>
+    <t>Thông báo lỗi "'.' bị sử dụng sai vị trí trong '.' "</t>
+  </si>
+  <si>
+    <t>Đăng ký thành công</t>
+  </si>
+  <si>
+    <t>Thông báo "sai vị trí"</t>
+  </si>
+  <si>
+    <t>B1: Nhập Email hợp lệ
+B2: Nhập password
+B3: Nhấn "Đăng nhập"</t>
+  </si>
+  <si>
+    <t>B1: Nhập Email chưa tồn tại
+B2: Nhập password
+B3: Nhấn "Đăng nhập"</t>
+  </si>
+  <si>
+    <t>B1: Nhập Email: tuyetmai99@gmail.com
+B2: Trống password
+B3: Nhấn "Đăng nhập"</t>
+  </si>
+  <si>
+    <t>B1: Bỏ trống Email
+B2: Nhập password
+B3: Nhấn "Đăng nhập"</t>
+  </si>
+  <si>
+    <t>B1: Nhập Email hợp lệ
+B2: Nhập password hợp lệ
+B3: Nhấn "Đăng nhập"</t>
+  </si>
+  <si>
+    <t>Hệ thống hiện danh sách sản phẩm chứa từ khóa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hệ thống hiện sản phẩm chứa từ khóa </t>
+  </si>
+  <si>
+    <t>Hiển thị sản phẩm có tên chuẩn</t>
+  </si>
+  <si>
+    <t>Trống số điện thoại</t>
+  </si>
+  <si>
+    <t>Người dùng truy cập vào trang web và thêm sản phẩm từ trang chủ vào giỏ hàng</t>
+  </si>
+  <si>
+    <t>B1: Click vào thanh tìm kiếm
+B2: Nhập từ khóa 1 phần
+B3: Nhấn Enter hoặc biểu tượng tìm kiếm</t>
+  </si>
+  <si>
+    <t>B1: Click vào thanh tìm kiếm
+B2: Nhập: ELA301 
+B3: Nhấn Enter hoặc biểu tượng tìm kiếm</t>
+  </si>
+  <si>
+    <t>B1: Click vào thanh tìm kiếm
+B2: Nhập tên đầy đủ
+B3: Nhấn Enter hoặc biểu tượng tìm kiếm</t>
+  </si>
+  <si>
+    <t>B1: Click vào thanh tìm kiếm
+B2: Nhập ký hiệu đặc biệt
+B3: Nhấn Enter hoặc biểu tượng tìm kiếm</t>
+  </si>
+  <si>
+    <t>B1: Click vào thanh tìm kiếm
+B2: Bỏ trống 
+B3: Nhấn Enter hoặc biểu tượng tìm kiếm</t>
+  </si>
+  <si>
+    <t>B1: Click vào thanh tìm kiếm
+B2: Nhập từ không có trong sản phẩm
+B3: Nhấn Enter hoặc biểu tượng tìm kiếm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B1: Nhập họ tên, email, địa chỉ, ghi chú hợp lệ
+B2: Nhập số điện thoại &lt;10 số
+B3: Nhấn "Thanh toán" 
 </t>
   </si>
   <si>
-    <t>Hệ thống hiện danh sách sản phẩm chứa "cao gót 7cm"</t>
-  </si>
-  <si>
-    <t>Tìm kiếm sản phẩm theo mã sản phẩm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">B1: Truy cập vào website https://ella.vn/
-B2: Click vào thanh tìm kiếm
-B3: Nhập: ELA301 
-B4: Nhấn Enter hoặc biểu tượng tìm kiếm
+    <t xml:space="preserve">B1: Nhập họ tên, email, địa chỉ, ghi chú hợp lệ
+B2: Nhập số điện thoại &gt;10 số
+B3: Nhấn "Thanh toán" 
 </t>
   </si>
   <si>
-    <t>Hệ thống hiện  sản phẩm chứa từ khóa "ELA301"</t>
-  </si>
-  <si>
-    <t>Tìm kiếm sản phẩm với tên đầy đủ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">B1: Truy cập vào website https://ella.vn/
-B2: Click vào thanh tìm kiếm
-B3: Nhập: Giày sandal công sở ELLA 7cm thanh lịch cuốn hút ELA662
-B4: Nhấn Enter hoặc biểu tượng tìm kiếm
+    <t xml:space="preserve">B1: Nhập họ tên, email, địa chỉ, ghi chú hợp lệ
+B2: Nhập số điện thoại chứa ký tự đặc biệt
+B3: Nhấn "Thanh toán" 
 </t>
   </si>
   <si>
-    <t>Hiển thị duy nhất 1 sản phẩm có tên "Giày sandal công sở ELLA 7cm thanh lịch cuốn hút ELA662"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">B1: Truy cập vào website https://ella.vn/
-B2: Click vào thanh tìm kiếm
-B3: Nhập: !@#$
-B4: Nhấn Enter hoặc biểu tượng tìm kiếm
+    <t xml:space="preserve">B1: Nhập họ tên, email, địa chỉ, ghi chú hợp lệ
+B2: Nhập số điện thoại chứa chữ
+B3: Nhấn "Thanh toán" 
 </t>
   </si>
   <si>
-    <t>Hệ thống hiện danh sách sản phẩm ngẫu nhiên</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bỏ trống </t>
-  </si>
-  <si>
-    <t xml:space="preserve">B1: Truy cập vào website https://ella.vn/
-B2: Click vào thanh tìm kiếm
-B3: Nhập: 
-B4: Nhấn Enter hoặc biểu tượng tìm kiếm
+    <t xml:space="preserve">B1: Nhập họ tên, email, địa chỉ, ghi chú hợp lệ
+B2: Bỏ trống số điện thoại 
+B3: Nhấn "Thanh toán" 
 </t>
   </si>
   <si>
-    <t>Hệ thống hiện thông báo "Vui lòng điền vào trường này"</t>
-  </si>
-  <si>
-    <t>Tìm kiếm với từ khóa không có trong sản phẩm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">B1: Truy cập vào website https://ella.vn/
-B2: Click vào thanh tìm kiếm
-B3: Nhập: móng
-B4: Nhấn Enter hoặc biểu tượng tìm kiếm
+    <t xml:space="preserve">B1: Nhập họ tên, số điện thoại, email, ghi chú hợp lệ
+B2: Bỏ trống địa chỉ
+B3: Nhấn "Thanh toán" 
 </t>
   </si>
   <si>
-    <t>Hệ thống không hiện sản phẩm nào</t>
-  </si>
-  <si>
-    <t>Sai số điện thoại &lt;10 số</t>
-  </si>
-  <si>
-    <t>Sai số điện thoại &gt;10 số</t>
-  </si>
-  <si>
-    <t xml:space="preserve">B1: Truy cập vào website https://ella.vn/
-B2: Chọn sản phẩm
-B3: Chọn "Thêm vào giỏ"
-B4: Nhập họ tên: Linh
-B5: Nhập Số điện thoại: 0123456789
-B6: Nhập email: linhnguyen@gmail.com
-B7: Nhập địa chỉ: 123 Main St, City
-B8: Nhập ghi chú: Giao giờ hành chính
-B9: Nhấn "Thanh toán" 
+    <t xml:space="preserve">B1: Nhập họ tên, số điện thoại, địa chỉ, ghi chú hợp lệ
+B2: Nhập email thiếu sau @
+B3: Nhấn "Thanh toán" 
 </t>
   </si>
   <si>
-    <t>Hệ thống thông báo "Đơn hàng của bạn đã được gửi đi"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">B1: Truy cập vào website https://ella.vn/
-B2: Chọn sản phẩm
-B3: Chọn "Thêm vào giỏ"
-B4: Nhập họ tên: Linh
-B5: Nhập Số điện thoại: 
-B6: Nhập email: linhnguyen@gmail.com
-B7: Nhập địa chỉ: 123 Main St, City
-B8: Nhập ghi chú: Giao giờ hành chính
-B9: Nhấn "Thanh toán" 
+    <t xml:space="preserve">B1: Nhập họ tên, số điện thoại, địa chỉ, ghi chú hợp lệ
+B2: Nhập email thiếu trước @
+B3: Nhấn "Thanh toán" 
 </t>
   </si>
   <si>
-    <t>Hệ thống thông báo "Vui lòng điền vào trường này"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">B1: Truy cập vào website https://ella.vn/
-B2: Chọn sản phẩm
-B3: Chọn "Thêm vào giỏ"
-B4: Nhập họ tên: Linh
-B5: Nhập Số điện thoại: 0123456789
-B6: Nhập email: linhnguyen@gmail.com
-B7: Nhập địa chỉ: 
-B8: Nhập ghi chú: Giao giờ hành chính
-B9: Nhấn "Thanh toán" 
+    <t xml:space="preserve">B1: Nhập họ tên, số điện thoại, địa chỉ, ghi chú hợp lệ
+B2: Nhập email thiếu @
+B3: Nhấn "Thanh toán" 
 </t>
   </si>
   <si>
-    <t xml:space="preserve">B1: Truy cập vào website https://ella.vn/
-B2: Chọn sản phẩm
-B3: Chọn "Thêm vào giỏ"
-B4: Nhập họ tên: Linh
-B5: Nhập Số điện thoại: 012345678999
-B6: Nhập email: linhnguyen@gmail.com
-B7: Nhập địa chỉ: 123 Main St, City
-B8: Nhập ghi chú: Giao giờ hành chính
-B9: Nhấn "Thanh toán" 
+    <t xml:space="preserve">B1: Nhập họ tên, số điện thoại, địa chỉ, ghi chú hợp lệ
+B2: Nhập email sai vị trí dấu '.'
+B3: Nhấn "Thanh toán" 
 </t>
   </si>
   <si>
-    <t>Hệ thống thông báo "Vui lòng nhập ít nhất một số điện thoại bạn đang sử dụng"</t>
-  </si>
-  <si>
-    <t>cập nhật thành công</t>
-  </si>
-  <si>
-    <t xml:space="preserve">B1: Truy cập vào website https://ella.vn/
-B2: Đăng nhập tài khoản
-B3: Chọn Tài khoản
-B4: Nhập Họ và tên: Hoang Nguyen
-B5: Nhập SDT: 0123456789
-B6: Địa chỉ: 123 Main St, Hanoi
-B7: Nhấn Cập nhật
+    <t xml:space="preserve">
+Hệ thống thông báo "Cập nhật thông tin tài khoản thành công"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+Hệ thống thông báo "Vui lòng nhập ít nhất một số điện thoại bạn đang sử dụng"</t>
+  </si>
+  <si>
+    <t>Người dùng đã đăng nhập vào trang web và đang ở trong thông tin tài khoản</t>
+  </si>
+  <si>
+    <t>B1: Nhập Họ và tên, số điện thoại, địa chỉ hợp lệ
+B2: Nhấn Cập nhật</t>
+  </si>
+  <si>
+    <t>B1: Nhập Họ và tên, địa chỉ hợp lệ
+B2: Bỏ trống số điện thoại
+B3: Nhấn Cập nhật</t>
+  </si>
+  <si>
+    <t>B1: Nhập số điện thoại, địa chỉ hợp lệ
+B2: Bỏ trống Họ và tên
+B3: Nhấn Cập nhật</t>
+  </si>
+  <si>
+    <t>B1: Nhập Họ và tên, địa chỉ hợp lệ
+B2: Bỏ trống địa chỉ hợp lệ
+B3: Nhấn Cập nhật</t>
+  </si>
+  <si>
+    <t>B1: Nhập Họ và tên, địa chỉ hợp lệ
+B2: Nhập số điện thoại chứa ký tự đặc biệt
+B3: Nhấn Cập nhật</t>
+  </si>
+  <si>
+    <t>B1: Nhập Họ và tên, địa chỉ hợp lệ
+B2: Nhập số điện thoại &lt; 10 số
+B3: Nhấn Cập nhật</t>
+  </si>
+  <si>
+    <t>B1: Nhập Họ và tên, địa chỉ hợp lệ
+B2: Nhập số điện thoại &gt;10 số
+B3: Nhấn Cập nhật</t>
+  </si>
+  <si>
+    <t>B1: Nhập Họ và tên, địa chỉ hợp lệ
+B2: Nhập số điện thoại chứ chữ
+B3: Nhấn Cập nhật</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+Hệ thống thông báo "Đơn hàng của bạn đã được gửi đi"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+Hệ thống thông báo "Vui lòng nhập ít nhất một số điện thoại bạn đang sử dụng"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+Hệ thống thông báo "Vui lòng điền vào trường này"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+Hệ thống thông báo "Vui lòng nhập phần đứng sau @"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+Hệ thống thông báo "Vui lòng"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+Hệ thống thông báo "Vui lòng nhập phần đứng trước @"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+Hệ thống thông báo "Vui lòng nhập bao gồm '@' trong địa chỉ email"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+Hệ thống thông báo "'.' bị sai vị trí trong '.'"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+Hệ thống thông báo "sai vị trí"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B1: Nhập họ tên, số điện thoại, địa chỉ, ghi chú hợp lệ
+B2: Nhập email thiếu @
+B3: Nhấn "Thanh toán" </t>
+  </si>
+  <si>
+    <t xml:space="preserve">B1: Nhập họ tên, số điện thoại, địa chỉ, ghi chú hợp lệ
+B2: Nhập email sai vị trí dấu '.'
+B3: Nhấn "Thanh toán" </t>
+  </si>
+  <si>
+    <t xml:space="preserve">B1: Nhập họ tên, số điện thoại, địa chỉ, ghi chú hợp lệ
+B2: Nhập email thiếu trước @
+B3: Nhấn "Thanh toán" </t>
+  </si>
+  <si>
+    <t xml:space="preserve">B1: Nhập họ tên, số điện thoại, địa chỉ, ghi chú hợp lệ
+B2: Nhập email thiếu sau @
+B3: Nhấn "Thanh toán" </t>
+  </si>
+  <si>
+    <t xml:space="preserve">B1: Nhập họ tên, số điện thoại, email, ghi chú hợp lệ
+B2: Bỏ trống địa chỉ
+B3: Nhấn "Thanh toán" </t>
+  </si>
+  <si>
+    <t xml:space="preserve">B1: Nhập họ tên, email, địa chỉ, ghi chú hợp lệ
+B2: Bỏ trống số điện thoại 
+B3: Nhấn "Thanh toán" </t>
+  </si>
+  <si>
+    <t xml:space="preserve">B1: Nhập họ tên, email, địa chỉ, ghi chú hợp lệ
+B2: Nhập số điện thoại chứa chữ
+B3: Nhấn "Thanh toán" </t>
+  </si>
+  <si>
+    <t xml:space="preserve">B1: Nhập họ tên, email, địa chỉ, ghi chú hợp lệ
+B2: Nhập số điện thoại chứa ký tự đặc biệt
+B3: Nhấn "Thanh toán" </t>
+  </si>
+  <si>
+    <t xml:space="preserve">B1: Nhập họ tên, email, địa chỉ, ghi chú hợp lệ
+B2: Nhập số điện thoại &gt;10 số
+B3: Nhấn "Thanh toán" </t>
+  </si>
+  <si>
+    <t xml:space="preserve">B1: Nhập họ tên, email, địa chỉ, ghi chú hợp lệ
+B2: Nhập số điện thoại &lt;10 số
+B3: Nhấn "Thanh toán" </t>
+  </si>
+  <si>
+    <t xml:space="preserve">B1: Nhập họ tên, số điện thoại, email, địa chỉ, ghi chú hợp lệ
+B2: Nhấn "Thanh toán" </t>
+  </si>
+  <si>
+    <t xml:space="preserve">B1: Nhập họ tên, số điện thoại, email, địa chỉ, ghi chú hợp lệ
+B2: Nhấn "Thanh toán" 
 </t>
   </si>
   <si>
-    <t xml:space="preserve">B1: Truy cập vào website https://ella.vn/
-B2: Đăng nhập tài khoản
-B3: Chọn Tài khoản
-B4: Nhập Họ và tên: Hoang Nguyen
-B5: Nhập SDT: 
-B6: Địa chỉ: 123 Main St, Hanoi
-B7: Nhấn Cập nhật
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">B1: Truy cập vào website https://ella.vn/
-B2: Đăng nhập tài khoản
-B3: Chọn Tài khoản
-B4: Nhập Họ và tên:
-B5: Nhập SDT: 0123456789
-B6: Địa chỉ: 123 Main St, Hanoi
-B7: Nhấn Cập nhật
-</t>
-  </si>
-  <si>
-    <t>Bỏ trống địa chỉ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">B1: Truy cập vào website https://ella.vn/
-B2: Đăng nhập tài khoản
-B3: Chọn Tài khoản
-B4: Nhập Họ và tên: Hoang Nguyen
-B5: Nhập SDT: 0123456789
-B6: Địa chỉ:
-B7: Nhấn Cập nhật
-</t>
-  </si>
-  <si>
-    <t>Số điện thoại &lt; 10 số</t>
-  </si>
-  <si>
-    <t xml:space="preserve">B1: Truy cập vào website https://ella.vn/
-B2: Đăng nhập tài khoản
-B3: Chọn Tài khoản
-B4: Nhập Họ và tên: Hoang Nguyen
-B5: Nhập SDT: 012345678999
-B6: Địa chỉ: 123 Main St, Hanoi
-B7: Nhấn Cập nhật
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">B1: Truy cập vào website https://ella.vn/
-B2: Đăng nhập tài khoản
-B3: Chọn Tài khoản
-B4: Nhập Họ và tên: Hoang Nguyen
-B5: Nhập SDT: 01234
-B6: Địa chỉ: 123 Main St, Hanoi
-B7: Nhấn Cập nhật
-</t>
-  </si>
-  <si>
-    <t>email thiếu trước @</t>
-  </si>
-  <si>
-    <t>vị trí dấu '.' sai</t>
-  </si>
-  <si>
-    <t>Hiển thị trang chủ Ella
-Hiển thị giao diện đăng ký
-Thông báo lỗi "'.' bị sử dụng sai vị trí trong '.' "</t>
-  </si>
-  <si>
-    <t>Hiển thị trang chủ Ella
-Hiển thị giao diện đăng ký
-Thông báo "sai vị trí"</t>
-  </si>
-  <si>
-    <t>register_Auto_Test_3_20260519_001508.png</t>
-  </si>
-  <si>
-    <t xml:space="preserve">B1: Truy cập vào website https://ella.vn/
-B2: Chọn sản phẩm
-B3: Chọn "Thêm vào giỏ"
-B4: Nhập họ tên: Linh
-B5: Nhập Số điện thoại: 01234
-B6: Nhập email: linhnguyen@gmail.com
-B7: Nhập địa chỉ: 123 Main St, City
-B8: Nhập ghi chú: Giao giờ hành chính
-B9: Nhấn "Thanh toán" 
-</t>
-  </si>
-  <si>
-    <t>Sai số điện thoại chứa ký tự đặc biệt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">B1: Truy cập vào website https://ella.vn/
-B2: Chọn sản phẩm
-B3: Chọn "Thêm vào giỏ"
-B4: Nhập họ tên: Linh
-B5: Nhập Số điện thoại: 012345679@
-B6: Nhập email: linhnguyen@gmail.com
-B7: Nhập địa chỉ: 123 Main St, City
-B8: Nhập ghi chú: Giao giờ hành chính
-B9: Nhấn "Thanh toán" 
-</t>
-  </si>
-  <si>
-    <t>Email thiếu phần sau @</t>
-  </si>
-  <si>
-    <t>Email thiếu phần trước @</t>
-  </si>
-  <si>
-    <t>Email thiếu @</t>
-  </si>
-  <si>
-    <t xml:space="preserve">B1: Truy cập vào website https://ella.vn/
-B2: Chọn sản phẩm
-B3: Chọn "Thêm vào giỏ"
-B4: Nhập họ tên: Linh
-B5: Nhập Số điện thoại: 0123456789
-B6: Nhập email: linhnguyen@
-B7: Nhập địa chỉ: 123 Main St, City
-B8: Nhập ghi chú: Giao giờ hành chính
-B9: Nhấn "Thanh toán" 
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">B1: Truy cập vào website https://ella.vn/
-B2: Chọn sản phẩm
-B3: Chọn "Thêm vào giỏ"
-B4: Nhập họ tên: Linh
-B5: Nhập Số điện thoại: 0123456789
-B6: Nhập email: @gmail.com
-B7: Nhập địa chỉ: 123 Main St, City
-B8: Nhập ghi chú: Giao giờ hành chính
-B9: Nhấn "Thanh toán" 
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">B1: Truy cập vào website https://ella.vn/
-B2: Chọn sản phẩm
-B3: Chọn "Thêm vào giỏ"
-B4: Nhập họ tên: Linh
-B5: Nhập Số điện thoại: 0123456789
-B6: Nhập email: linhnguyen@gmail.
-B7: Nhập địa chỉ: 123 Main St, City
-B8: Nhập ghi chú: Giao giờ hành chính
-B9: Nhấn "Thanh toán" 
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">B1: Truy cập vào website https://ella.vn/
-B2: Chọn sản phẩm
-B3: Chọn "Thêm vào giỏ"
-B4: Nhập họ tên: Linh
-B5: Nhập Số điện thoại: 0123456789
-B6: Nhập email: linhnguyengmail
-B7: Nhập địa chỉ: 123 Main St, City
-B8: Nhập ghi chú: Giao giờ hành chính
-B9: Nhấn "Thanh toán" 
-</t>
-  </si>
-  <si>
-    <t>Hệ thống thông báo "Vui lòng nhập phần đứng sau @"</t>
-  </si>
-  <si>
-    <t>Hệ thống thông báo "Vui lòng"</t>
-  </si>
-  <si>
-    <t>Hệ thống thông báo "sai vị trí"</t>
-  </si>
-  <si>
-    <t>Hệ thống thông báo "Vui lòng nhập phần đứng trước @"</t>
-  </si>
-  <si>
-    <t>Hệ thống thông báo "Vui lòng nhập bao gồm '@' trong địa chỉ email"</t>
-  </si>
-  <si>
-    <t>Hệ thống thông báo "'.' bị sai vị trí trong '.'"</t>
-  </si>
-  <si>
-    <t>order_Auto_Test_3_20260515_165252.png</t>
-  </si>
-  <si>
-    <t>Số điện thoại chứa ký tự đặc biệt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">B1: Truy cập vào website https://ella.vn/
-B2: Đăng nhập tài khoản
-B3: Chọn Tài khoản
-B4: Nhập Họ và tên: Hoang Nguyen
-B5: Nhập SDT: 012345678@
-B6: Địa chỉ: 123 Main St, Hanoi
-B7: Nhấn Cập nhật
-</t>
-  </si>
-  <si>
-    <t>Số điện thoại &gt; 10 số</t>
-  </si>
-  <si>
-    <t xml:space="preserve">B1: Truy cập vào website https://ella.vn/
-B2: Đăng nhập tài khoản
-B3: Chọn Tài khoản
-B4: Nhập Họ và tên: Hoang Nguyen
-B5: Nhập SDT: 012345678aa
-B6: Địa chỉ: 123 Main St, Hanoi
-B7: Nhấn Cập nhật
-</t>
-  </si>
-  <si>
-    <t>Số điện thoại chứa chữ</t>
-  </si>
-  <si>
-    <t>E2E_login_20260517_213426_5_.png</t>
-  </si>
-  <si>
-    <t>E2E_login_20260517_213426_6.png</t>
-  </si>
-  <si>
-    <t>E2E_login_20260517_213426_7.png</t>
-  </si>
-  <si>
-    <t>E2E_login_20260517_213426_8.png</t>
-  </si>
-  <si>
-    <t xml:space="preserve">B1: Truy cập vào website https://ella.vn/
-B2: Đăng nhập tài khoản
-B3: Tim kiếm sản phẩm
-B4: Chọn sản phẩm
-B5: Chọn "Thêm vào giỏ"
-B6: Nhập họ tên: Linh
-B7: Nhập Số điện thoại: 0123456789
-B8: Nhập email: linhnguyen@gmail.com
-B9: Nhập địa chỉ: 123 Main St, City
-B10: Nhập ghi chú: Giao giờ hành chính
-B11: Nhấn "Thanh toán" 
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">B1: Truy cập vào website https://ella.vn/
-B2: Đăng nhập tài khoản
-B3: Tim kiếm sản phẩm
-B4: Chọn sản phẩm
-B5: Chọn "Thêm vào giỏ"
-B6: Nhập họ tên: Linh
-B7: Nhập Số điện thoại: 01234
-B8: Nhập email: linhnguyen@gmail.com
-B9: Nhập địa chỉ: 123 Main St, City
-B10: Nhập ghi chú: Giao giờ hành chính
-B11: Nhấn "Thanh toán" 
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">B1: Truy cập vào website https://ella.vn/
-B2: Đăng nhập tài khoản
-B3: Tim kiếm sản phẩm
-B4: Chọn sản phẩm
-B5: Chọn "Thêm vào giỏ"
-B6: Nhập họ tên: Linh
-B7: Nhập Số điện thoại: 012345678999
-B8: Nhập email: linhnguyen@gmail.com
-B9: Nhập địa chỉ: 123 Main St, City
-B10: Nhập ghi chú: Giao giờ hành chính
-B11: Nhấn "Thanh toán" 
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">B1: Truy cập vào website https://ella.vn/
-B2: Đăng nhập tài khoản
-B3: Tim kiếm sản phẩm
-B4: Chọn sản phẩm
-B5: Chọn "Thêm vào giỏ"
-B6: Nhập họ tên: Linh
-B7: Nhập Số điện thoại: 012345679@
-B8: Nhập email: linhnguyen@gmail.com
-B9: Nhập địa chỉ: 123 Main St, City
-B10: Nhập ghi chú: Giao giờ hành chính
-B11: Nhấn "Thanh toán" 
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">B1: Truy cập vào website https://ella.vn/
-B2: Đăng nhập tài khoản
-B3: Tim kiếm sản phẩm
-B4: Chọn sản phẩm
-B5: Chọn "Thêm vào giỏ"
-B6: Nhập họ tên: Linh
-B7: Nhập Số điện thoại: 
-B8: Nhập email: linhnguyen@gmail.com
-B9: Nhập địa chỉ: 123 Main St, City
-B10: Nhập ghi chú: Giao giờ hành chính
-B11: Nhấn "Thanh toán" 
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">B1: Truy cập vào website https://ella.vn/
-B2: Đăng nhập tài khoản
-B3: Tim kiếm sản phẩm
-B4: Chọn sản phẩm
-B5: Chọn "Thêm vào giỏ"
-B6: Nhập họ tên: Linh
-B7: Nhập Số điện thoại: 0123456789
-B8: Nhập email: linhnguyen@gmail.com
-B9: Nhập địa chỉ: 
-B10: Nhập ghi chú: Giao giờ hành chính
-B11: Nhấn "Thanh toán" 
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">B1: Truy cập vào website https://ella.vn/
-B2: Đăng nhập tài khoản
-B3: Tim kiếm sản phẩm
-B4: Chọn sản phẩm
-B5: Chọn "Thêm vào giỏ"
-B6: Nhập họ tên: Linh
-B7: Nhập Số điện thoại: 0123456789
-B8: Nhập email: linhnguyen@
-B9: Nhập địa chỉ: 123 Main St, City
-B10: Nhập ghi chú: Giao giờ hành chính
-B11: Nhấn "Thanh toán" 
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">B1: Truy cập vào website https://ella.vn/
-B2: Đăng nhập tài khoản
-B3: Tim kiếm sản phẩm
-B4: Chọn sản phẩm
-B5: Chọn "Thêm vào giỏ"
-B6: Nhập họ tên: Linh
-B7: Nhập Số điện thoại: 0123456789
-B8: Nhập email: @gmail.com
-B9: Nhập địa chỉ: 123 Main St, City
-B10: Nhập ghi chú: Giao giờ hành chính
-B11: Nhấn "Thanh toán" 
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">B1: Truy cập vào website https://ella.vn/
-B2: Đăng nhập tài khoản
-B3: Tim kiếm sản phẩm
-B4: Chọn sản phẩm
-B5: Chọn "Thêm vào giỏ"
-B6: Nhập họ tên: Linh
-B7: Nhập Số điện thoại: 0123456789
-B8: Nhập email: linhnguyengmail
-B9: Nhập địa chỉ: 123 Main St, City
-B10: Nhập ghi chú: Giao giờ hành chính
-B11: Nhấn "Thanh toán" 
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">B1: Truy cập vào website https://ella.vn/
-B2: Đăng nhập tài khoản
-B3: Tim kiếm sản phẩm
-B4: Chọn sản phẩm
-B5: Chọn "Thêm vào giỏ"
-B6: Nhập họ tên: Linh
-B7: Nhập Số điện thoại: 0123456789
-B8: Nhập email: linhnguyen@gmail.
-B9: Nhập địa chỉ: 123 Main St, City
-B10: Nhập ghi chú: Giao giờ hành chính
-B11: Nhấn "Thanh toán" 
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chức năng </t>
-  </si>
-  <si>
-    <t>Đăng ký</t>
-  </si>
-  <si>
-    <t>Đăng nhập</t>
-  </si>
-  <si>
-    <t>Tìm kiếm</t>
-  </si>
-  <si>
-    <t>Đặt hàng</t>
-  </si>
-  <si>
-    <t>E2E Đặt hàng</t>
-  </si>
-  <si>
-    <t>Profile</t>
-  </si>
-  <si>
-    <t>Sai số điện thoại chứa chữ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">B1: Truy cập vào website https://ella.vn/
-B2: Đăng nhập tài khoản
-B3: Tim kiếm sản phẩm
-B4: Chọn sản phẩm
-B5: Chọn "Thêm vào giỏ"
-B6: Nhập họ tên: Linh
-B7: Nhập Số điện thoại: 012345679a
-B8: Nhập email: linhnguyen@gmail.com
-B9: Nhập địa chỉ: 123 Main St, City
-B10: Nhập ghi chú: Giao giờ hành chính
-B11: Nhấn "Thanh toán" 
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">B1: Truy cập vào website https://ella.vn/
-B2: Chọn sản phẩm
-B3: Chọn "Thêm vào giỏ"
-B4: Nhập họ tên: Linh
-B5: Nhập Số điện thoại: 012345679a
-B6: Nhập email: linhnguyen@gmail.com
-B7: Nhập địa chỉ: 123 Main St, City
-B8: Nhập ghi chú: Giao giờ hành chính
-B9: Nhấn "Thanh toán" 
-</t>
-  </si>
-  <si>
-    <t>Số lượng kịch bản</t>
-  </si>
-  <si>
-    <t>Tổng số</t>
-  </si>
-  <si>
-    <t>Đăng nhập thành công
-Tìm kiếm đúng sản phẩm
-Hệ thống thông báo "Đơn hàng của bạn đã được gửi đi"</t>
-  </si>
-  <si>
-    <t>Đăng nhập thành công
-Tìm kiếm đúng sản phẩm
-Hệ thống thông báo "Vui lòng nhập ít nhất một số điện thoại bạn đang sử dụng"</t>
-  </si>
-  <si>
-    <t>Đăng nhập thành công
-Tìm kiếm đúng sản phẩm
-Hệ thống thông báo "Vui lòng điền vào trường này"</t>
-  </si>
-  <si>
-    <t>Đăng nhập thành công
-Tìm kiếm đúng sản phẩm
-Hệ thống thông báo "Vui lòng nhập phần đứng sau @"</t>
-  </si>
-  <si>
-    <t>Đăng nhập thành công
-Tìm kiếm đúng sản phẩm
-Hệ thống thông báo "Vui lòng nhập phần đứng trước @"</t>
-  </si>
-  <si>
-    <t>Đăng nhập thành công
-Tìm kiếm đúng sản phẩm
-Hệ thống thông báo "Vui lòng nhập bao gồm '@' trong địa chỉ email"</t>
-  </si>
-  <si>
-    <t>Đăng nhập thành công
-Tìm kiếm đúng sản phẩm
-Hệ thống thông báo "'.' bị sai vị trí trong '.'"</t>
-  </si>
-  <si>
-    <t>Đăng nhập thành công
-Tìm kiếm đúng sản phẩm
-Hệ thống thông báo "Vui lòng"</t>
-  </si>
-  <si>
-    <t>Đăng nhập thành công
-Tìm kiếm đúng sản phẩm
-Hệ thống thông báo "sai vị trí"</t>
-  </si>
-  <si>
-    <t>Đăng nhập thành công
-Hệ thống thông báo "Cập nhật thông tin tài khoản thành công"</t>
-  </si>
-  <si>
-    <t>Đăng nhập thành công
-Hệ thống thông báo "Vui lòng nhập ít nhất một số điện thoại bạn đang sử dụng"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">B1: Truy cập vào website https://ella.vn/
-B2: Chọn chức năng đăng ký
-B3: Nhập email: ngminhtu@gmail.com
-B4: Nhập mật khẩu: ngmi
-B5: Nhập xác nhânh mật khẩu: ngmi
-B6: Nhấn "Đăng ký" </t>
-  </si>
-  <si>
-    <t xml:space="preserve">B1: Truy cập vào website https://ella.vn/
-B2: Chọn chức năng đăng ký
-B3: Nhập email: hoanganh@gmail.com
-B4: Nhập mật khẩu: hoanganh
-B5: Nhập xác nhânh mật khẩu: hoanganh1
-B6: Nhấn "Đăng ký" </t>
-  </si>
-  <si>
-    <t xml:space="preserve">B1: Truy cập vào website https://ella.vn/
-B2: Chọn chức năng đăng ký
-B3: Nhập email: 
-B4: Nhập mật khẩu: ngminhtu
-B5: Nhập xác nhânh mật khẩu: ngminhtu
-B6: Nhấn "Đăng ký" </t>
-  </si>
-  <si>
-    <t xml:space="preserve">B1: Truy cập vào website https://ella.vn/
-B2: Chọn chức năng đăng ký
-B3: Nhập email: ngminhtu@gmail.com
-B4: Nhập mật khẩu: 
-B5: Nhập xác nhânh mật khẩu: ngminhtu
-B6: Nhấn "Đăng ký" </t>
-  </si>
-  <si>
-    <t xml:space="preserve">B1: Truy cập vào website https://ella.vn/
-B2: Chọn chức năng đăng ký
-B3: Nhập email: ngminhtu@gmail.com
-B4: Nhập mật khẩu: ngminhtu
-B5: Nhập xác nhânh mật khẩu: 
-B6: Nhấn "Đăng ký" </t>
-  </si>
-  <si>
-    <t xml:space="preserve">B1: Truy cập vào website https://ella.vn/
-B2: Chọn chức năng đăng ký
-B3: Nhập email: ngminhtu.com
-B4: Nhập mật khẩu: ngminhtu
-B5: Nhập xác nhânh mật khẩu: ngminhtu
-B6: Nhấn "Đăng ký" </t>
-  </si>
-  <si>
-    <t xml:space="preserve">B1: Truy cập vào website https://ella.vn/
-B2: Chọn chức năng đăng ký
-B3: Nhập email: ngminhtu@
-B4: Nhập mật khẩu: ngminhtu
-B5: Nhập xác nhânh mật khẩu: ngminhtu
-B6: Nhấn "Đăng ký" </t>
-  </si>
-  <si>
-    <t xml:space="preserve">B1: Truy cập vào website https://ella.vn/
-B2: Chọn chức năng đăng ký
-B3: Nhập email: @gmail.com
-B4: Nhập mật khẩu: ngminhtu
-B5: Nhập xác nhânh mật khẩu: ngminhtu
-B6: Nhấn "Đăng ký" </t>
-  </si>
-  <si>
-    <t xml:space="preserve">B1: Truy cập vào website https://ella.vn/
-B2: Chọn chức năng đăng ký
-B3: Nhập email: ngminhtu@gmail.
-B4: Nhập mật khẩu: ngminhtu
-B5: Nhập xác nhânh mật khẩu: ngminhtu
-B6: Nhấn "Đăng ký" </t>
-  </si>
-  <si>
-    <t>Fail: 0</t>
+    <t>Người dùng đã đăng nhập tài khoản, tìm kiếm và thêm sản phẩm vào giỏ hàng</t>
   </si>
 </sst>
 </file>
@@ -1663,7 +1367,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="14.5">
       <c r="A1" s="18" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>0</v>
@@ -1726,160 +1430,160 @@
         <v>3</v>
       </c>
       <c r="B4" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="23" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" s="23" t="s">
+        <v>12</v>
+      </c>
+      <c r="E4" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="F4" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="C4" s="23" t="s">
+      <c r="G4" s="23" t="s">
         <v>15</v>
-      </c>
-      <c r="D4" s="23" t="s">
-        <v>16</v>
-      </c>
-      <c r="E4" s="23" t="s">
-        <v>17</v>
-      </c>
-      <c r="F4" s="23" t="s">
-        <v>18</v>
-      </c>
-      <c r="G4" s="23" t="s">
-        <v>19</v>
       </c>
       <c r="H4" s="23" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="50.25" customHeight="1">
+    <row r="5" spans="1:8" ht="40">
       <c r="A5" s="24" t="str">
         <f>"[DangNhap - " &amp; TEXT(ROW(A1), "00") &amp; "]"</f>
         <v>[DangNhap - 01]</v>
       </c>
       <c r="B5" s="25" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C5" s="25" t="s">
-        <v>7</v>
+        <v>81</v>
       </c>
       <c r="D5" s="19" t="s">
-        <v>41</v>
+        <v>110</v>
       </c>
       <c r="E5" s="19" t="s">
-        <v>47</v>
+        <v>82</v>
       </c>
       <c r="F5" s="19" t="s">
-        <v>47</v>
+        <v>82</v>
       </c>
       <c r="G5" s="24" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H5" s="26" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" ht="50">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="40">
       <c r="A6" s="24" t="str">
         <f t="shared" ref="A6:A9" si="0">"[DangNhap - " &amp; TEXT(ROW(A2), "00") &amp; "]"</f>
         <v>[DangNhap - 02]</v>
       </c>
       <c r="B6" s="27" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C6" s="25" t="s">
-        <v>7</v>
+        <v>81</v>
       </c>
       <c r="D6" s="19" t="s">
-        <v>42</v>
+        <v>111</v>
       </c>
       <c r="E6" s="19" t="s">
-        <v>47</v>
+        <v>82</v>
       </c>
       <c r="F6" s="19" t="s">
-        <v>47</v>
+        <v>82</v>
       </c>
       <c r="G6" s="24" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H6" s="26" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" ht="50">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="40">
       <c r="A7" s="24" t="str">
         <f t="shared" si="0"/>
         <v>[DangNhap - 03]</v>
       </c>
       <c r="B7" s="28" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C7" s="25" t="s">
-        <v>7</v>
+        <v>81</v>
       </c>
       <c r="D7" s="19" t="s">
-        <v>40</v>
+        <v>112</v>
       </c>
       <c r="E7" s="19" t="s">
-        <v>48</v>
+        <v>83</v>
       </c>
       <c r="F7" s="19" t="s">
-        <v>48</v>
+        <v>83</v>
       </c>
       <c r="G7" s="24" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H7" s="26" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" ht="50">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="40">
       <c r="A8" s="24" t="str">
         <f t="shared" si="0"/>
         <v>[DangNhap - 04]</v>
       </c>
       <c r="B8" s="25" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C8" s="25" t="s">
-        <v>7</v>
+        <v>81</v>
       </c>
       <c r="D8" s="19" t="s">
-        <v>43</v>
+        <v>113</v>
       </c>
       <c r="E8" s="19" t="s">
-        <v>48</v>
+        <v>83</v>
       </c>
       <c r="F8" s="19" t="s">
-        <v>48</v>
+        <v>83</v>
       </c>
       <c r="G8" s="24" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H8" s="26" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" ht="50">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="40">
       <c r="A9" s="24" t="str">
         <f t="shared" si="0"/>
         <v>[DangNhap - 05]</v>
       </c>
       <c r="B9" s="28" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C9" s="25" t="s">
-        <v>7</v>
+        <v>81</v>
       </c>
       <c r="D9" s="19" t="s">
-        <v>44</v>
+        <v>114</v>
       </c>
       <c r="E9" s="19" t="s">
-        <v>49</v>
+        <v>84</v>
       </c>
       <c r="F9" s="19" t="s">
-        <v>50</v>
+        <v>85</v>
       </c>
       <c r="G9" s="24" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H9" s="26" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -1922,20 +1626,20 @@
   <dimension ref="A1:I14"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="10"/>
   <cols>
-    <col min="1" max="1" width="12" style="1" customWidth="1"/>
-    <col min="2" max="2" width="18.54296875" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18" style="1" customWidth="1"/>
-    <col min="4" max="4" width="40.36328125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="10.90625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.7265625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.54296875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="31.26953125" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="30.36328125" style="1" customWidth="1"/>
     <col min="7" max="7" width="9.6328125" style="1" customWidth="1"/>
     <col min="8" max="8" width="7.90625" style="1" customWidth="1"/>
-    <col min="9" max="9" width="10.54296875" style="1" customWidth="1"/>
+    <col min="9" max="9" width="21" style="1" customWidth="1"/>
     <col min="10" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="14.5">
       <c r="A1" s="18" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>0</v>
@@ -1998,309 +1702,309 @@
         <v>3</v>
       </c>
       <c r="B4" s="23" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C4" s="23" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" s="23" t="s">
+        <v>12</v>
+      </c>
+      <c r="E4" s="30" t="s">
+        <v>31</v>
+      </c>
+      <c r="F4" s="30" t="s">
+        <v>32</v>
+      </c>
+      <c r="G4" s="23" t="s">
         <v>15</v>
-      </c>
-      <c r="D4" s="23" t="s">
-        <v>16</v>
-      </c>
-      <c r="E4" s="30" t="s">
-        <v>37</v>
-      </c>
-      <c r="F4" s="30" t="s">
-        <v>38</v>
-      </c>
-      <c r="G4" s="23" t="s">
-        <v>19</v>
       </c>
       <c r="H4" s="23" t="s">
         <v>4</v>
       </c>
       <c r="I4" s="23" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" s="2" customFormat="1" ht="60">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" s="2" customFormat="1" ht="30">
       <c r="A5" s="19" t="str">
         <f>"[DangKy - " &amp; TEXT(ROW(A1),"00") &amp; "]"</f>
         <v>[DangKy - 01]</v>
       </c>
       <c r="B5" s="19" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="C5" s="31" t="s">
-        <v>8</v>
+        <v>91</v>
       </c>
       <c r="D5" s="19" t="s">
-        <v>46</v>
+        <v>92</v>
       </c>
       <c r="E5" s="19" t="s">
-        <v>51</v>
+        <v>102</v>
       </c>
       <c r="F5" s="19" t="s">
-        <v>51</v>
+        <v>102</v>
       </c>
       <c r="G5" s="19" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H5" s="27" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="I5" s="36"/>
     </row>
-    <row r="6" spans="1:9" ht="60">
+    <row r="6" spans="1:9" ht="30">
       <c r="A6" s="19" t="str">
         <f t="shared" ref="A6:A7" si="0">"[DangKy - " &amp; TEXT(ROW(A2),"00") &amp; "]"</f>
         <v>[DangKy - 02]</v>
       </c>
       <c r="B6" s="25" t="s">
-        <v>57</v>
+        <v>35</v>
       </c>
       <c r="C6" s="31" t="s">
-        <v>8</v>
+        <v>91</v>
       </c>
       <c r="D6" s="19" t="s">
-        <v>160</v>
+        <v>93</v>
       </c>
       <c r="E6" s="19" t="s">
-        <v>58</v>
+        <v>103</v>
       </c>
       <c r="F6" s="19" t="s">
-        <v>58</v>
+        <v>103</v>
       </c>
       <c r="G6" s="19" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H6" s="27" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="I6" s="37"/>
     </row>
-    <row r="7" spans="1:9" ht="60">
+    <row r="7" spans="1:9" ht="30">
       <c r="A7" s="19" t="str">
         <f t="shared" si="0"/>
         <v>[DangKy - 03]</v>
       </c>
       <c r="B7" s="19" t="s">
-        <v>59</v>
+        <v>86</v>
       </c>
       <c r="C7" s="31" t="s">
-        <v>8</v>
+        <v>91</v>
       </c>
       <c r="D7" s="19" t="s">
-        <v>161</v>
+        <v>94</v>
       </c>
       <c r="E7" s="19" t="s">
-        <v>60</v>
+        <v>104</v>
       </c>
       <c r="F7" s="19" t="s">
-        <v>61</v>
+        <v>108</v>
       </c>
       <c r="G7" s="35" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="H7" s="27" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="I7" s="38" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" ht="60">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="30">
       <c r="A8" s="19" t="str">
         <f>"[DangKy - " &amp; TEXT(ROW(A4),"00") &amp; "]"</f>
         <v>[DangKy - 04]</v>
       </c>
       <c r="B8" s="25" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="C8" s="31" t="s">
-        <v>8</v>
+        <v>91</v>
       </c>
       <c r="D8" s="19" t="s">
-        <v>162</v>
+        <v>95</v>
       </c>
       <c r="E8" s="19" t="s">
-        <v>52</v>
+        <v>105</v>
       </c>
       <c r="F8" s="19" t="s">
-        <v>52</v>
+        <v>105</v>
       </c>
       <c r="G8" s="19" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H8" s="27" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="I8" s="37"/>
     </row>
-    <row r="9" spans="1:9" ht="60">
+    <row r="9" spans="1:9" ht="30">
       <c r="A9" s="19" t="str">
         <f>"[DangKy - " &amp; TEXT(ROW(A5),"00") &amp; "]"</f>
         <v>[DangKy - 05]</v>
       </c>
       <c r="B9" s="25" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="C9" s="31" t="s">
-        <v>8</v>
+        <v>91</v>
       </c>
       <c r="D9" s="19" t="s">
-        <v>163</v>
+        <v>96</v>
       </c>
       <c r="E9" s="19" t="s">
-        <v>52</v>
+        <v>105</v>
       </c>
       <c r="F9" s="19" t="s">
-        <v>52</v>
+        <v>105</v>
       </c>
       <c r="G9" s="19" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H9" s="27" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="I9" s="37"/>
     </row>
-    <row r="10" spans="1:9" ht="60">
+    <row r="10" spans="1:9" ht="30">
       <c r="A10" s="19" t="str">
-        <f>"[DangKy - " &amp; TEXT(ROW(A7),"00") &amp; "]"</f>
+        <f t="shared" ref="A10:A14" si="1">"[DangKy - " &amp; TEXT(ROW(A6),"00") &amp; "]"</f>
+        <v>[DangKy - 06]</v>
+      </c>
+      <c r="B10" s="25" t="s">
+        <v>87</v>
+      </c>
+      <c r="C10" s="31" t="s">
+        <v>91</v>
+      </c>
+      <c r="D10" s="19" t="s">
+        <v>97</v>
+      </c>
+      <c r="E10" s="19" t="s">
+        <v>105</v>
+      </c>
+      <c r="F10" s="19" t="s">
+        <v>105</v>
+      </c>
+      <c r="G10" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="H10" s="27" t="s">
+        <v>16</v>
+      </c>
+      <c r="I10" s="37"/>
+    </row>
+    <row r="11" spans="1:9" ht="30">
+      <c r="A11" s="19" t="str">
+        <f t="shared" si="1"/>
         <v>[DangKy - 07]</v>
       </c>
-      <c r="B10" s="25" t="s">
-        <v>53</v>
-      </c>
-      <c r="C10" s="31" t="s">
-        <v>8</v>
-      </c>
-      <c r="D10" s="19" t="s">
-        <v>164</v>
-      </c>
-      <c r="E10" s="19" t="s">
-        <v>52</v>
-      </c>
-      <c r="F10" s="19" t="s">
-        <v>52</v>
-      </c>
-      <c r="G10" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="H10" s="27" t="s">
-        <v>20</v>
-      </c>
-      <c r="I10" s="37"/>
-    </row>
-    <row r="11" spans="1:9" ht="60">
-      <c r="A11" s="19" t="str">
-        <f>"[DangKy - " &amp; TEXT(ROW(A6),"00") &amp; "]"</f>
-        <v>[DangKy - 06]</v>
-      </c>
       <c r="B11" s="25" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C11" s="31" t="s">
-        <v>8</v>
+        <v>91</v>
       </c>
       <c r="D11" s="19" t="s">
-        <v>165</v>
+        <v>98</v>
       </c>
       <c r="E11" s="19" t="s">
-        <v>55</v>
+        <v>106</v>
       </c>
       <c r="F11" s="19" t="s">
-        <v>55</v>
+        <v>106</v>
       </c>
       <c r="G11" s="19" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H11" s="27" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="I11" s="34"/>
     </row>
-    <row r="12" spans="1:9" ht="60">
+    <row r="12" spans="1:9" ht="30">
       <c r="A12" s="19" t="str">
-        <f t="shared" ref="A12:A14" si="1">"[DangKy - " &amp; TEXT(ROW(A8),"00") &amp; "]"</f>
+        <f t="shared" si="1"/>
         <v>[DangKy - 08]</v>
       </c>
       <c r="B12" s="25" t="s">
-        <v>56</v>
+        <v>88</v>
       </c>
       <c r="C12" s="31" t="s">
-        <v>8</v>
+        <v>91</v>
       </c>
       <c r="D12" s="19" t="s">
-        <v>166</v>
+        <v>99</v>
       </c>
       <c r="E12" s="19" t="s">
-        <v>55</v>
+        <v>106</v>
       </c>
       <c r="F12" s="19" t="s">
-        <v>55</v>
+        <v>106</v>
       </c>
       <c r="G12" s="19" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H12" s="27" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="I12" s="34"/>
     </row>
-    <row r="13" spans="1:9" ht="68" customHeight="1">
+    <row r="13" spans="1:9" ht="30">
       <c r="A13" s="19" t="str">
         <f t="shared" si="1"/>
         <v>[DangKy - 09]</v>
       </c>
       <c r="B13" s="19" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="C13" s="31" t="s">
-        <v>8</v>
+        <v>91</v>
       </c>
       <c r="D13" s="19" t="s">
-        <v>167</v>
+        <v>100</v>
       </c>
       <c r="E13" s="19" t="s">
-        <v>55</v>
+        <v>106</v>
       </c>
       <c r="F13" s="19" t="s">
-        <v>55</v>
+        <v>106</v>
       </c>
       <c r="G13" s="19" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H13" s="27" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="I13" s="37"/>
     </row>
-    <row r="14" spans="1:9" ht="68" customHeight="1">
+    <row r="14" spans="1:9" ht="30">
       <c r="A14" s="19" t="str">
         <f t="shared" si="1"/>
         <v>[DangKy - 10]</v>
       </c>
       <c r="B14" s="19" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="C14" s="31" t="s">
-        <v>8</v>
+        <v>91</v>
       </c>
       <c r="D14" s="19" t="s">
-        <v>168</v>
+        <v>101</v>
       </c>
       <c r="E14" s="19" t="s">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="F14" s="19" t="s">
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="G14" s="19" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H14" s="27" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="I14" s="37"/>
     </row>
@@ -2323,7 +2027,7 @@
     <col min="1" max="1" width="12.36328125" style="8" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="17.54296875" style="8" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="18" style="8" customWidth="1"/>
-    <col min="4" max="4" width="40.1796875" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="28" style="8" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="30.36328125" style="8" customWidth="1"/>
     <col min="7" max="7" width="9.6328125" style="8" customWidth="1"/>
     <col min="8" max="8" width="6.54296875" style="8" customWidth="1"/>
@@ -2332,7 +2036,7 @@
   <sheetData>
     <row r="1" spans="1:9" ht="14.5">
       <c r="A1" s="18" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>0</v>
@@ -2392,193 +2096,193 @@
         <v>3</v>
       </c>
       <c r="B4" s="23" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="C4" s="23" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" s="23" t="s">
+        <v>12</v>
+      </c>
+      <c r="E4" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="F4" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="G4" s="23" t="s">
         <v>15</v>
-      </c>
-      <c r="D4" s="23" t="s">
-        <v>169</v>
-      </c>
-      <c r="E4" s="23" t="s">
-        <v>17</v>
-      </c>
-      <c r="F4" s="23" t="s">
-        <v>18</v>
-      </c>
-      <c r="G4" s="23" t="s">
-        <v>19</v>
       </c>
       <c r="H4" s="23" t="s">
         <v>4</v>
       </c>
       <c r="I4" s="29" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" s="15" customFormat="1" ht="50">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" s="15" customFormat="1" ht="30">
       <c r="A5" s="19" t="str">
         <f>"[TimKiemSP - " &amp; TEXT(ROW(A1),"00") &amp; "]"</f>
         <v>[TimKiemSP - 01]</v>
       </c>
       <c r="B5" s="28" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="C5" s="31" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D5" s="19" t="s">
-        <v>62</v>
+        <v>120</v>
       </c>
       <c r="E5" s="19" t="s">
-        <v>63</v>
+        <v>115</v>
       </c>
       <c r="F5" s="19" t="s">
-        <v>63</v>
+        <v>115</v>
       </c>
       <c r="G5" s="19" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H5" s="32" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" ht="50">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="30">
       <c r="A6" s="19" t="str">
         <f t="shared" ref="A6:A10" si="0">"[TimKiemSP - " &amp; TEXT(ROW(A2),"00") &amp; "]"</f>
         <v>[TimKiemSP - 02]</v>
       </c>
       <c r="B6" s="28" t="s">
-        <v>64</v>
+        <v>36</v>
       </c>
       <c r="C6" s="31" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D6" s="19" t="s">
-        <v>65</v>
+        <v>121</v>
       </c>
       <c r="E6" s="19" t="s">
-        <v>66</v>
+        <v>116</v>
       </c>
       <c r="F6" s="19" t="s">
-        <v>66</v>
+        <v>116</v>
       </c>
       <c r="G6" s="19" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H6" s="32" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" ht="60">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="30">
       <c r="A7" s="19" t="str">
         <f t="shared" si="0"/>
         <v>[TimKiemSP - 03]</v>
       </c>
       <c r="B7" s="28" t="s">
-        <v>67</v>
+        <v>37</v>
       </c>
       <c r="C7" s="31" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D7" s="19" t="s">
-        <v>68</v>
+        <v>122</v>
       </c>
       <c r="E7" s="19" t="s">
-        <v>69</v>
+        <v>117</v>
       </c>
       <c r="F7" s="19" t="s">
-        <v>69</v>
+        <v>117</v>
       </c>
       <c r="G7" s="19" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H7" s="32" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="I7" s="16"/>
     </row>
-    <row r="8" spans="1:9" ht="50">
+    <row r="8" spans="1:9" ht="30">
       <c r="A8" s="19" t="str">
         <f>"[TimKiemSP - " &amp; TEXT(ROW(C4),"00") &amp; "]"</f>
         <v>[TimKiemSP - 04]</v>
       </c>
       <c r="B8" s="28" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="C8" s="31" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D8" s="19" t="s">
-        <v>70</v>
+        <v>123</v>
       </c>
       <c r="E8" s="19" t="s">
-        <v>71</v>
+        <v>38</v>
       </c>
       <c r="F8" s="19" t="s">
-        <v>71</v>
+        <v>38</v>
       </c>
       <c r="G8" s="19" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H8" s="32" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="I8" s="17"/>
     </row>
-    <row r="9" spans="1:9" ht="50">
+    <row r="9" spans="1:9" ht="30">
       <c r="A9" s="19" t="str">
         <f t="shared" si="0"/>
         <v>[TimKiemSP - 05]</v>
       </c>
       <c r="B9" s="28" t="s">
-        <v>72</v>
+        <v>39</v>
       </c>
       <c r="C9" s="31" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D9" s="19" t="s">
-        <v>73</v>
+        <v>124</v>
       </c>
       <c r="E9" s="19" t="s">
-        <v>74</v>
+        <v>40</v>
       </c>
       <c r="F9" s="19" t="s">
-        <v>74</v>
+        <v>40</v>
       </c>
       <c r="G9" s="28" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H9" s="32" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="I9" s="16"/>
     </row>
-    <row r="10" spans="1:9" ht="50">
+    <row r="10" spans="1:9" ht="30">
       <c r="A10" s="19" t="str">
         <f t="shared" si="0"/>
         <v>[TimKiemSP - 06]</v>
       </c>
       <c r="B10" s="28" t="s">
-        <v>75</v>
+        <v>41</v>
       </c>
       <c r="C10" s="31" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D10" s="19" t="s">
-        <v>76</v>
+        <v>125</v>
       </c>
       <c r="E10" s="19" t="s">
-        <v>77</v>
+        <v>42</v>
       </c>
       <c r="F10" s="19" t="s">
-        <v>77</v>
+        <v>42</v>
       </c>
       <c r="G10" s="28" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H10" s="32" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -2623,21 +2327,21 @@
   <sheetData>
     <row r="4" spans="6:9" ht="14.5">
       <c r="F4" s="40" t="s">
-        <v>137</v>
+        <v>71</v>
       </c>
       <c r="G4" s="40" t="s">
-        <v>147</v>
+        <v>79</v>
       </c>
       <c r="H4" s="40" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="I4" s="40" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="6:9" ht="14.5">
       <c r="F5" s="39" t="s">
-        <v>138</v>
+        <v>72</v>
       </c>
       <c r="G5" s="41">
         <v>10</v>
@@ -2651,7 +2355,7 @@
     </row>
     <row r="6" spans="6:9" ht="14.5">
       <c r="F6" s="45" t="s">
-        <v>139</v>
+        <v>73</v>
       </c>
       <c r="G6" s="46">
         <v>5</v>
@@ -2665,7 +2369,7 @@
     </row>
     <row r="7" spans="6:9" ht="14.5">
       <c r="F7" s="39" t="s">
-        <v>140</v>
+        <v>74</v>
       </c>
       <c r="G7" s="41">
         <v>6</v>
@@ -2679,7 +2383,7 @@
     </row>
     <row r="8" spans="6:9" ht="14.5">
       <c r="F8" s="45" t="s">
-        <v>141</v>
+        <v>75</v>
       </c>
       <c r="G8" s="46">
         <v>11</v>
@@ -2693,7 +2397,7 @@
     </row>
     <row r="9" spans="6:9" ht="14.5">
       <c r="F9" s="39" t="s">
-        <v>142</v>
+        <v>76</v>
       </c>
       <c r="G9" s="41">
         <v>11</v>
@@ -2707,7 +2411,7 @@
     </row>
     <row r="10" spans="6:9" ht="14.5">
       <c r="F10" s="45" t="s">
-        <v>143</v>
+        <v>77</v>
       </c>
       <c r="G10" s="46">
         <v>8</v>
@@ -2721,7 +2425,7 @@
     </row>
     <row r="11" spans="6:9" ht="14.5">
       <c r="F11" s="43" t="s">
-        <v>148</v>
+        <v>80</v>
       </c>
       <c r="G11" s="44">
         <f>SUM(G5:G10)</f>
@@ -2747,19 +2451,19 @@
   <dimension ref="A1:I15"/>
   <sheetFormatPr defaultRowHeight="13"/>
   <cols>
-    <col min="1" max="1" width="15.26953125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="20.453125" customWidth="1"/>
-    <col min="3" max="3" width="16.453125" customWidth="1"/>
+    <col min="1" max="1" width="12.36328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.7265625" customWidth="1"/>
+    <col min="3" max="3" width="19.26953125" customWidth="1"/>
     <col min="4" max="4" width="36.453125" customWidth="1"/>
     <col min="5" max="5" width="23.6328125" customWidth="1"/>
     <col min="6" max="6" width="32.81640625" customWidth="1"/>
     <col min="8" max="8" width="4.453125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.7265625" customWidth="1"/>
+    <col min="9" max="9" width="19.08984375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="14.5">
       <c r="A1" s="18" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>0</v>
@@ -2822,337 +2526,337 @@
         <v>3</v>
       </c>
       <c r="B4" s="23" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="C4" s="23" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" s="23" t="s">
+        <v>12</v>
+      </c>
+      <c r="E4" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="F4" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="G4" s="23" t="s">
         <v>15</v>
-      </c>
-      <c r="D4" s="23" t="s">
-        <v>16</v>
-      </c>
-      <c r="E4" s="23" t="s">
-        <v>17</v>
-      </c>
-      <c r="F4" s="23" t="s">
-        <v>18</v>
-      </c>
-      <c r="G4" s="23" t="s">
-        <v>19</v>
       </c>
       <c r="H4" s="23" t="s">
         <v>4</v>
       </c>
       <c r="I4" s="23" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" ht="100">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="40">
       <c r="A5" s="19" t="str">
         <f>"[ThanhToan - " &amp; TEXT(ROW(A1),"00") &amp; "]"</f>
         <v>[ThanhToan - 01]</v>
       </c>
       <c r="B5" s="19" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="C5" s="31" t="s">
-        <v>10</v>
+        <v>119</v>
       </c>
       <c r="D5" s="19" t="s">
-        <v>80</v>
+        <v>167</v>
       </c>
       <c r="E5" s="19" t="s">
-        <v>81</v>
+        <v>45</v>
       </c>
       <c r="F5" s="19" t="s">
-        <v>81</v>
+        <v>45</v>
       </c>
       <c r="G5" s="19" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H5" s="19" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="I5" s="33"/>
     </row>
-    <row r="6" spans="1:9" ht="100">
+    <row r="6" spans="1:9" ht="40">
       <c r="A6" s="19" t="str">
         <f t="shared" ref="A6:A15" si="0">"[ThanhToan - " &amp; TEXT(ROW(A2),"00") &amp; "]"</f>
         <v>[ThanhToan - 02]</v>
       </c>
       <c r="B6" s="19" t="s">
-        <v>78</v>
+        <v>43</v>
       </c>
       <c r="C6" s="31" t="s">
-        <v>10</v>
+        <v>119</v>
       </c>
       <c r="D6" s="19" t="s">
-        <v>101</v>
+        <v>126</v>
       </c>
       <c r="E6" s="19" t="s">
-        <v>86</v>
+        <v>47</v>
       </c>
       <c r="F6" s="19" t="s">
-        <v>86</v>
+        <v>47</v>
       </c>
       <c r="G6" s="19" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H6" s="19" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="I6" s="33"/>
     </row>
-    <row r="7" spans="1:9" ht="100">
+    <row r="7" spans="1:9" ht="40">
       <c r="A7" s="19" t="str">
         <f t="shared" si="0"/>
         <v>[ThanhToan - 03]</v>
       </c>
       <c r="B7" s="19" t="s">
-        <v>79</v>
+        <v>44</v>
       </c>
       <c r="C7" s="31" t="s">
-        <v>10</v>
+        <v>119</v>
       </c>
       <c r="D7" s="19" t="s">
-        <v>85</v>
+        <v>127</v>
       </c>
       <c r="E7" s="19" t="s">
-        <v>86</v>
+        <v>47</v>
       </c>
       <c r="F7" s="19" t="s">
-        <v>81</v>
+        <v>45</v>
       </c>
       <c r="G7" s="35" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="H7" s="19" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="I7" s="38" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" ht="100">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="40">
       <c r="A8" s="19" t="str">
         <f t="shared" si="0"/>
         <v>[ThanhToan - 04]</v>
       </c>
       <c r="B8" s="19" t="s">
-        <v>102</v>
+        <v>53</v>
       </c>
       <c r="C8" s="31" t="s">
-        <v>10</v>
+        <v>119</v>
       </c>
       <c r="D8" s="19" t="s">
-        <v>103</v>
+        <v>128</v>
       </c>
       <c r="E8" s="19" t="s">
-        <v>86</v>
+        <v>47</v>
       </c>
       <c r="F8" s="19" t="s">
-        <v>86</v>
+        <v>47</v>
       </c>
       <c r="G8" s="19" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H8" s="19" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="I8" s="33"/>
     </row>
-    <row r="9" spans="1:9" ht="100">
+    <row r="9" spans="1:9" ht="40">
       <c r="A9" s="19" t="str">
         <f t="shared" si="0"/>
         <v>[ThanhToan - 05]</v>
       </c>
       <c r="B9" s="19" t="s">
-        <v>144</v>
+        <v>78</v>
       </c>
       <c r="C9" s="31" t="s">
-        <v>10</v>
+        <v>119</v>
       </c>
       <c r="D9" s="19" t="s">
-        <v>146</v>
+        <v>129</v>
       </c>
       <c r="E9" s="19" t="s">
-        <v>86</v>
+        <v>47</v>
       </c>
       <c r="F9" s="19" t="s">
-        <v>86</v>
+        <v>47</v>
       </c>
       <c r="G9" s="19" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H9" s="19" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="I9" s="33"/>
     </row>
-    <row r="10" spans="1:9" ht="100">
+    <row r="10" spans="1:9" ht="40">
       <c r="A10" s="19" t="str">
         <f t="shared" si="0"/>
         <v>[ThanhToan - 06]</v>
       </c>
       <c r="B10" s="19" t="s">
-        <v>32</v>
+        <v>118</v>
       </c>
       <c r="C10" s="31" t="s">
-        <v>10</v>
+        <v>119</v>
       </c>
       <c r="D10" s="19" t="s">
-        <v>82</v>
+        <v>130</v>
       </c>
       <c r="E10" s="19" t="s">
-        <v>83</v>
+        <v>46</v>
       </c>
       <c r="F10" s="19" t="s">
-        <v>83</v>
+        <v>46</v>
       </c>
       <c r="G10" s="19" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H10" s="19" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="I10" s="33"/>
     </row>
-    <row r="11" spans="1:9" ht="100">
+    <row r="11" spans="1:9" ht="40">
       <c r="A11" s="19" t="str">
         <f t="shared" si="0"/>
         <v>[ThanhToan - 07]</v>
       </c>
       <c r="B11" s="19" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="C11" s="31" t="s">
-        <v>10</v>
+        <v>119</v>
       </c>
       <c r="D11" s="19" t="s">
-        <v>84</v>
+        <v>131</v>
       </c>
       <c r="E11" s="19" t="s">
-        <v>83</v>
+        <v>46</v>
       </c>
       <c r="F11" s="19" t="s">
-        <v>83</v>
+        <v>46</v>
       </c>
       <c r="G11" s="19" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H11" s="19" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="I11" s="33"/>
     </row>
-    <row r="12" spans="1:9" ht="100">
+    <row r="12" spans="1:9" ht="40">
       <c r="A12" s="19" t="str">
         <f t="shared" si="0"/>
         <v>[ThanhToan - 08]</v>
       </c>
       <c r="B12" s="19" t="s">
-        <v>104</v>
+        <v>54</v>
       </c>
       <c r="C12" s="31" t="s">
-        <v>10</v>
+        <v>119</v>
       </c>
       <c r="D12" s="19" t="s">
-        <v>107</v>
+        <v>132</v>
       </c>
       <c r="E12" s="19" t="s">
-        <v>111</v>
+        <v>57</v>
       </c>
       <c r="F12" s="19" t="s">
-        <v>112</v>
+        <v>58</v>
       </c>
       <c r="G12" s="19" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H12" s="19" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="I12" s="33"/>
     </row>
-    <row r="13" spans="1:9" ht="100">
+    <row r="13" spans="1:9" ht="40">
       <c r="A13" s="19" t="str">
         <f t="shared" si="0"/>
         <v>[ThanhToan - 09]</v>
       </c>
       <c r="B13" s="19" t="s">
-        <v>105</v>
+        <v>55</v>
       </c>
       <c r="C13" s="31" t="s">
-        <v>10</v>
+        <v>119</v>
       </c>
       <c r="D13" s="19" t="s">
-        <v>108</v>
+        <v>133</v>
       </c>
       <c r="E13" s="19" t="s">
-        <v>114</v>
+        <v>60</v>
       </c>
       <c r="F13" s="19" t="s">
-        <v>112</v>
+        <v>58</v>
       </c>
       <c r="G13" s="19" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H13" s="19" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="I13" s="33"/>
     </row>
-    <row r="14" spans="1:9" ht="100">
+    <row r="14" spans="1:9" ht="40">
       <c r="A14" s="19" t="str">
         <f t="shared" si="0"/>
         <v>[ThanhToan - 10]</v>
       </c>
       <c r="B14" s="19" t="s">
-        <v>106</v>
+        <v>56</v>
       </c>
       <c r="C14" s="31" t="s">
-        <v>10</v>
+        <v>119</v>
       </c>
       <c r="D14" s="19" t="s">
-        <v>110</v>
+        <v>134</v>
       </c>
       <c r="E14" s="19" t="s">
-        <v>115</v>
+        <v>61</v>
       </c>
       <c r="F14" s="19" t="s">
-        <v>112</v>
+        <v>58</v>
       </c>
       <c r="G14" s="19" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H14" s="19" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="I14" s="33"/>
     </row>
-    <row r="15" spans="1:9" ht="100">
+    <row r="15" spans="1:9" ht="40">
       <c r="A15" s="19" t="str">
         <f t="shared" si="0"/>
         <v>[ThanhToan - 11]</v>
       </c>
       <c r="B15" s="19" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="C15" s="31" t="s">
-        <v>10</v>
+        <v>119</v>
       </c>
       <c r="D15" s="19" t="s">
-        <v>109</v>
+        <v>135</v>
       </c>
       <c r="E15" s="19" t="s">
-        <v>116</v>
+        <v>62</v>
       </c>
       <c r="F15" s="19" t="s">
-        <v>113</v>
+        <v>59</v>
       </c>
       <c r="G15" s="19" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H15" s="19" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="I15" s="33"/>
     </row>
@@ -3179,11 +2883,12 @@
     <col min="5" max="5" width="28.1796875" customWidth="1"/>
     <col min="6" max="6" width="19.453125" customWidth="1"/>
     <col min="8" max="8" width="5.90625" customWidth="1"/>
+    <col min="9" max="9" width="18.1796875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="14.5">
       <c r="A1" s="18" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>0</v>
@@ -3246,260 +2951,260 @@
         <v>3</v>
       </c>
       <c r="B4" s="23" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="C4" s="23" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" s="23" t="s">
+        <v>12</v>
+      </c>
+      <c r="E4" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="F4" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="G4" s="23" t="s">
         <v>15</v>
-      </c>
-      <c r="D4" s="23" t="s">
-        <v>16</v>
-      </c>
-      <c r="E4" s="23" t="s">
-        <v>17</v>
-      </c>
-      <c r="F4" s="23" t="s">
-        <v>18</v>
-      </c>
-      <c r="G4" s="23" t="s">
-        <v>19</v>
       </c>
       <c r="H4" s="23" t="s">
         <v>4</v>
       </c>
       <c r="I4" s="23" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" ht="80">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="40">
       <c r="A5" s="19" t="str">
         <f>"[ChangeProfile - " &amp; TEXT(ROW(A1),"00") &amp; "]"</f>
         <v>[ChangeProfile - 01]</v>
       </c>
       <c r="B5" s="19" t="s">
-        <v>87</v>
+        <v>48</v>
       </c>
       <c r="C5" s="31" t="s">
-        <v>13</v>
+        <v>138</v>
       </c>
       <c r="D5" s="19" t="s">
-        <v>88</v>
+        <v>139</v>
       </c>
       <c r="E5" s="19" t="s">
-        <v>158</v>
+        <v>136</v>
       </c>
       <c r="F5" s="19" t="s">
-        <v>158</v>
+        <v>136</v>
       </c>
       <c r="G5" s="19" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H5" s="19" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="I5" s="34"/>
     </row>
-    <row r="6" spans="1:9" ht="80">
+    <row r="6" spans="1:9" ht="40">
       <c r="A6" s="19" t="str">
         <f t="shared" ref="A6:A12" si="0">"[ChangeProfile - " &amp; TEXT(ROW(A2),"00") &amp; "]"</f>
         <v>[ChangeProfile - 02]</v>
       </c>
       <c r="B6" s="19" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="C6" s="31" t="s">
-        <v>13</v>
+        <v>138</v>
       </c>
       <c r="D6" s="19" t="s">
-        <v>89</v>
+        <v>140</v>
       </c>
       <c r="E6" s="19" t="s">
-        <v>158</v>
+        <v>136</v>
       </c>
       <c r="F6" s="19" t="s">
-        <v>158</v>
+        <v>136</v>
       </c>
       <c r="G6" s="19" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H6" s="19" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="I6" s="34"/>
     </row>
-    <row r="7" spans="1:9" ht="80">
+    <row r="7" spans="1:9" ht="40">
       <c r="A7" s="19" t="str">
         <f t="shared" si="0"/>
         <v>[ChangeProfile - 03]</v>
       </c>
       <c r="B7" s="19" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="C7" s="31" t="s">
-        <v>13</v>
+        <v>138</v>
       </c>
       <c r="D7" s="19" t="s">
-        <v>90</v>
+        <v>141</v>
       </c>
       <c r="E7" s="19" t="s">
-        <v>158</v>
+        <v>136</v>
       </c>
       <c r="F7" s="19" t="s">
-        <v>158</v>
+        <v>136</v>
       </c>
       <c r="G7" s="19" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H7" s="19" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="I7" s="34"/>
     </row>
-    <row r="8" spans="1:9" ht="80">
+    <row r="8" spans="1:9" ht="40">
       <c r="A8" s="19" t="str">
         <f t="shared" si="0"/>
         <v>[ChangeProfile - 04]</v>
       </c>
       <c r="B8" s="19" t="s">
-        <v>91</v>
+        <v>49</v>
       </c>
       <c r="C8" s="31" t="s">
-        <v>13</v>
+        <v>138</v>
       </c>
       <c r="D8" s="19" t="s">
-        <v>92</v>
+        <v>142</v>
       </c>
       <c r="E8" s="19" t="s">
-        <v>158</v>
+        <v>136</v>
       </c>
       <c r="F8" s="19" t="s">
-        <v>158</v>
+        <v>136</v>
       </c>
       <c r="G8" s="19" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H8" s="19" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="I8" s="34"/>
     </row>
-    <row r="9" spans="1:9" ht="80">
+    <row r="9" spans="1:9" ht="40">
       <c r="A9" s="19" t="str">
         <f t="shared" si="0"/>
         <v>[ChangeProfile - 05]</v>
       </c>
       <c r="B9" s="19" t="s">
-        <v>118</v>
+        <v>64</v>
       </c>
       <c r="C9" s="31" t="s">
-        <v>13</v>
+        <v>138</v>
       </c>
       <c r="D9" s="19" t="s">
-        <v>119</v>
+        <v>143</v>
       </c>
       <c r="E9" s="19" t="s">
-        <v>159</v>
+        <v>137</v>
       </c>
       <c r="F9" s="19" t="s">
-        <v>158</v>
+        <v>136</v>
       </c>
       <c r="G9" s="35" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="H9" s="19" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="I9" s="38" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" ht="80">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="40">
       <c r="A10" s="19" t="str">
         <f t="shared" si="0"/>
         <v>[ChangeProfile - 06]</v>
       </c>
       <c r="B10" s="19" t="s">
-        <v>93</v>
+        <v>50</v>
       </c>
       <c r="C10" s="31" t="s">
-        <v>13</v>
+        <v>138</v>
       </c>
       <c r="D10" s="19" t="s">
-        <v>95</v>
+        <v>144</v>
       </c>
       <c r="E10" s="19" t="s">
-        <v>159</v>
+        <v>137</v>
       </c>
       <c r="F10" s="19" t="s">
-        <v>158</v>
+        <v>136</v>
       </c>
       <c r="G10" s="35" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="H10" s="19" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="I10" s="38" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" ht="80">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="40">
       <c r="A11" s="19" t="str">
         <f t="shared" si="0"/>
         <v>[ChangeProfile - 07]</v>
       </c>
       <c r="B11" s="19" t="s">
-        <v>120</v>
+        <v>65</v>
       </c>
       <c r="C11" s="31" t="s">
-        <v>13</v>
+        <v>138</v>
       </c>
       <c r="D11" s="19" t="s">
-        <v>94</v>
+        <v>145</v>
       </c>
       <c r="E11" s="19" t="s">
-        <v>159</v>
+        <v>137</v>
       </c>
       <c r="F11" s="19" t="s">
-        <v>158</v>
+        <v>136</v>
       </c>
       <c r="G11" s="35" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="H11" s="19" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="I11" s="38" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" ht="80">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="40">
       <c r="A12" s="19" t="str">
         <f t="shared" si="0"/>
         <v>[ChangeProfile - 08]</v>
       </c>
       <c r="B12" s="19" t="s">
-        <v>122</v>
+        <v>66</v>
       </c>
       <c r="C12" s="31" t="s">
-        <v>13</v>
+        <v>138</v>
       </c>
       <c r="D12" s="19" t="s">
-        <v>121</v>
+        <v>146</v>
       </c>
       <c r="E12" s="19" t="s">
-        <v>159</v>
+        <v>137</v>
       </c>
       <c r="F12" s="19" t="s">
-        <v>158</v>
+        <v>136</v>
       </c>
       <c r="G12" s="35" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="H12" s="19" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="I12" s="38" t="s">
-        <v>126</v>
+        <v>70</v>
       </c>
     </row>
   </sheetData>
@@ -3522,18 +3227,19 @@
   <dimension ref="A1:I15"/>
   <sheetFormatPr defaultRowHeight="13"/>
   <cols>
-    <col min="1" max="1" width="11.6328125" customWidth="1"/>
+    <col min="1" max="1" width="15.6328125" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
-    <col min="3" max="3" width="13.54296875" customWidth="1"/>
+    <col min="3" max="3" width="19.90625" customWidth="1"/>
     <col min="4" max="4" width="28.08984375" customWidth="1"/>
-    <col min="5" max="5" width="20.54296875" customWidth="1"/>
-    <col min="6" max="6" width="18.6328125" customWidth="1"/>
+    <col min="5" max="5" width="29.453125" customWidth="1"/>
+    <col min="6" max="6" width="22.36328125" customWidth="1"/>
     <col min="7" max="7" width="5.54296875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.6328125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="14.5">
       <c r="A1" s="18" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>0</v>
@@ -3596,337 +3302,337 @@
         <v>3</v>
       </c>
       <c r="B4" s="23" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="C4" s="23" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" s="23" t="s">
+        <v>12</v>
+      </c>
+      <c r="E4" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="F4" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="G4" s="23" t="s">
         <v>15</v>
-      </c>
-      <c r="D4" s="23" t="s">
-        <v>16</v>
-      </c>
-      <c r="E4" s="23" t="s">
-        <v>17</v>
-      </c>
-      <c r="F4" s="23" t="s">
-        <v>18</v>
-      </c>
-      <c r="G4" s="23" t="s">
-        <v>19</v>
       </c>
       <c r="H4" s="23" t="s">
         <v>4</v>
       </c>
       <c r="I4" s="23" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" ht="120">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="40">
       <c r="A5" s="19" t="str">
-        <f>"[ThanhToan - " &amp; TEXT(ROW(A1),"00") &amp; "]"</f>
-        <v>[ThanhToan - 01]</v>
+        <f>"[E2E_ThanhToan - " &amp; TEXT(ROW(A1),"00") &amp; "]"</f>
+        <v>[E2E_ThanhToan - 01]</v>
       </c>
       <c r="B5" s="19" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="C5" s="31" t="s">
-        <v>10</v>
+        <v>168</v>
       </c>
       <c r="D5" s="19" t="s">
-        <v>127</v>
+        <v>166</v>
       </c>
       <c r="E5" s="19" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="F5" s="19" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="G5" s="19" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H5" s="19" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="I5" s="33"/>
     </row>
-    <row r="6" spans="1:9" ht="120">
+    <row r="6" spans="1:9" ht="50">
       <c r="A6" s="19" t="str">
-        <f t="shared" ref="A6:A15" si="0">"[ThanhToan - " &amp; TEXT(ROW(A2),"00") &amp; "]"</f>
-        <v>[ThanhToan - 02]</v>
+        <f t="shared" ref="A6:A15" si="0">"[E2E_ThanhToan - " &amp; TEXT(ROW(A2),"00") &amp; "]"</f>
+        <v>[E2E_ThanhToan - 02]</v>
       </c>
       <c r="B6" s="19" t="s">
-        <v>78</v>
+        <v>43</v>
       </c>
       <c r="C6" s="31" t="s">
-        <v>10</v>
+        <v>168</v>
       </c>
       <c r="D6" s="19" t="s">
-        <v>128</v>
+        <v>165</v>
       </c>
       <c r="E6" s="19" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="F6" s="19" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="G6" s="19" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H6" s="19" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="I6" s="33"/>
     </row>
-    <row r="7" spans="1:9" ht="120">
+    <row r="7" spans="1:9" ht="43.5">
       <c r="A7" s="19" t="str">
         <f t="shared" si="0"/>
-        <v>[ThanhToan - 03]</v>
+        <v>[E2E_ThanhToan - 03]</v>
       </c>
       <c r="B7" s="19" t="s">
-        <v>79</v>
+        <v>44</v>
       </c>
       <c r="C7" s="31" t="s">
-        <v>10</v>
+        <v>168</v>
       </c>
       <c r="D7" s="19" t="s">
-        <v>129</v>
+        <v>164</v>
       </c>
       <c r="E7" s="19" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="F7" s="19" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="G7" s="35" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="H7" s="19" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="I7" s="38" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" ht="120">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="50">
       <c r="A8" s="19" t="str">
         <f t="shared" si="0"/>
-        <v>[ThanhToan - 04]</v>
+        <v>[E2E_ThanhToan - 04]</v>
       </c>
       <c r="B8" s="19" t="s">
-        <v>102</v>
+        <v>53</v>
       </c>
       <c r="C8" s="31" t="s">
-        <v>10</v>
+        <v>168</v>
       </c>
       <c r="D8" s="19" t="s">
-        <v>130</v>
+        <v>163</v>
       </c>
       <c r="E8" s="19" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="F8" s="19" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="G8" s="19" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H8" s="19" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="I8" s="33"/>
     </row>
-    <row r="9" spans="1:9" ht="120">
+    <row r="9" spans="1:9" ht="50">
       <c r="A9" s="19" t="str">
         <f t="shared" si="0"/>
-        <v>[ThanhToan - 05]</v>
+        <v>[E2E_ThanhToan - 05]</v>
       </c>
       <c r="B9" s="19" t="s">
-        <v>144</v>
+        <v>78</v>
       </c>
       <c r="C9" s="31" t="s">
-        <v>10</v>
+        <v>168</v>
       </c>
       <c r="D9" s="19" t="s">
-        <v>145</v>
+        <v>162</v>
       </c>
       <c r="E9" s="19" t="s">
+        <v>148</v>
+      </c>
+      <c r="F9" s="19" t="s">
+        <v>148</v>
+      </c>
+      <c r="G9" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="H9" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="I9" s="33"/>
+    </row>
+    <row r="10" spans="1:9" ht="40">
+      <c r="A10" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v>[E2E_ThanhToan - 06]</v>
+      </c>
+      <c r="B10" s="19" t="s">
+        <v>26</v>
+      </c>
+      <c r="C10" s="31" t="s">
+        <v>168</v>
+      </c>
+      <c r="D10" s="19" t="s">
+        <v>161</v>
+      </c>
+      <c r="E10" s="19" t="s">
+        <v>149</v>
+      </c>
+      <c r="F10" s="19" t="s">
+        <v>149</v>
+      </c>
+      <c r="G10" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="H10" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="I10" s="33"/>
+    </row>
+    <row r="11" spans="1:9" ht="40">
+      <c r="A11" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v>[E2E_ThanhToan - 07]</v>
+      </c>
+      <c r="B11" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="C11" s="31" t="s">
+        <v>168</v>
+      </c>
+      <c r="D11" s="19" t="s">
+        <v>160</v>
+      </c>
+      <c r="E11" s="19" t="s">
+        <v>149</v>
+      </c>
+      <c r="F11" s="19" t="s">
+        <v>149</v>
+      </c>
+      <c r="G11" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="H11" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="I11" s="33"/>
+    </row>
+    <row r="12" spans="1:9" ht="40">
+      <c r="A12" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v>[E2E_ThanhToan - 08]</v>
+      </c>
+      <c r="B12" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="C12" s="31" t="s">
+        <v>168</v>
+      </c>
+      <c r="D12" s="19" t="s">
+        <v>159</v>
+      </c>
+      <c r="E12" s="19" t="s">
         <v>150</v>
       </c>
-      <c r="F9" s="19" t="s">
-        <v>150</v>
-      </c>
-      <c r="G9" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="H9" s="19" t="s">
-        <v>20</v>
-      </c>
-      <c r="I9" s="33"/>
-    </row>
-    <row r="10" spans="1:9" ht="120">
-      <c r="A10" s="19" t="str">
-        <f>"[ThanhToan - " &amp; TEXT(ROW(A5),"00") &amp; "]"</f>
-        <v>[ThanhToan - 05]</v>
-      </c>
-      <c r="B10" s="19" t="s">
-        <v>32</v>
-      </c>
-      <c r="C10" s="31" t="s">
-        <v>10</v>
-      </c>
-      <c r="D10" s="19" t="s">
-        <v>131</v>
-      </c>
-      <c r="E10" s="19" t="s">
+      <c r="F12" s="19" t="s">
         <v>151</v>
       </c>
-      <c r="F10" s="19" t="s">
+      <c r="G12" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="H12" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="I12" s="33"/>
+    </row>
+    <row r="13" spans="1:9" ht="40">
+      <c r="A13" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v>[E2E_ThanhToan - 09]</v>
+      </c>
+      <c r="B13" s="19" t="s">
+        <v>55</v>
+      </c>
+      <c r="C13" s="31" t="s">
+        <v>168</v>
+      </c>
+      <c r="D13" s="19" t="s">
+        <v>158</v>
+      </c>
+      <c r="E13" s="19" t="s">
+        <v>152</v>
+      </c>
+      <c r="F13" s="19" t="s">
         <v>151</v>
       </c>
-      <c r="G10" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="H10" s="19" t="s">
-        <v>20</v>
-      </c>
-      <c r="I10" s="33"/>
-    </row>
-    <row r="11" spans="1:9" ht="120">
-      <c r="A11" s="19" t="str">
-        <f>"[ThanhToan - " &amp; TEXT(ROW(A6),"00") &amp; "]"</f>
-        <v>[ThanhToan - 06]</v>
-      </c>
-      <c r="B11" s="19" t="s">
-        <v>33</v>
-      </c>
-      <c r="C11" s="31" t="s">
-        <v>10</v>
-      </c>
-      <c r="D11" s="19" t="s">
-        <v>132</v>
-      </c>
-      <c r="E11" s="19" t="s">
-        <v>151</v>
-      </c>
-      <c r="F11" s="19" t="s">
-        <v>151</v>
-      </c>
-      <c r="G11" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="H11" s="19" t="s">
-        <v>20</v>
-      </c>
-      <c r="I11" s="33"/>
-    </row>
-    <row r="12" spans="1:9" ht="120">
-      <c r="A12" s="19" t="str">
-        <f>"[ThanhToan - " &amp; TEXT(ROW(A7),"00") &amp; "]"</f>
-        <v>[ThanhToan - 07]</v>
-      </c>
-      <c r="B12" s="19" t="s">
-        <v>104</v>
-      </c>
-      <c r="C12" s="31" t="s">
-        <v>10</v>
-      </c>
-      <c r="D12" s="19" t="s">
-        <v>133</v>
-      </c>
-      <c r="E12" s="19" t="s">
-        <v>152</v>
-      </c>
-      <c r="F12" s="19" t="s">
-        <v>156</v>
-      </c>
-      <c r="G12" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="H12" s="19" t="s">
-        <v>20</v>
-      </c>
-      <c r="I12" s="33"/>
-    </row>
-    <row r="13" spans="1:9" ht="120">
-      <c r="A13" s="19" t="str">
-        <f>"[ThanhToan - " &amp; TEXT(ROW(A8),"00") &amp; "]"</f>
-        <v>[ThanhToan - 08]</v>
-      </c>
-      <c r="B13" s="19" t="s">
-        <v>105</v>
-      </c>
-      <c r="C13" s="31" t="s">
-        <v>10</v>
-      </c>
-      <c r="D13" s="19" t="s">
-        <v>134</v>
-      </c>
-      <c r="E13" s="19" t="s">
-        <v>153</v>
-      </c>
-      <c r="F13" s="19" t="s">
-        <v>156</v>
-      </c>
       <c r="G13" s="19" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H13" s="19" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="I13" s="33"/>
     </row>
-    <row r="14" spans="1:9" ht="120">
+    <row r="14" spans="1:9" ht="40">
       <c r="A14" s="19" t="str">
         <f t="shared" si="0"/>
-        <v>[ThanhToan - 10]</v>
+        <v>[E2E_ThanhToan - 10]</v>
       </c>
       <c r="B14" s="19" t="s">
-        <v>106</v>
+        <v>56</v>
       </c>
       <c r="C14" s="31" t="s">
-        <v>10</v>
+        <v>168</v>
       </c>
       <c r="D14" s="19" t="s">
-        <v>135</v>
+        <v>156</v>
       </c>
       <c r="E14" s="19" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F14" s="19" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="G14" s="19" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H14" s="19" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="I14" s="33"/>
     </row>
-    <row r="15" spans="1:9" ht="120">
+    <row r="15" spans="1:9" ht="40">
       <c r="A15" s="19" t="str">
         <f t="shared" si="0"/>
-        <v>[ThanhToan - 11]</v>
+        <v>[E2E_ThanhToan - 11]</v>
       </c>
       <c r="B15" s="19" t="s">
-        <v>97</v>
+        <v>51</v>
       </c>
       <c r="C15" s="31" t="s">
-        <v>10</v>
+        <v>168</v>
       </c>
       <c r="D15" s="19" t="s">
-        <v>136</v>
+        <v>157</v>
       </c>
       <c r="E15" s="19" t="s">
+        <v>154</v>
+      </c>
+      <c r="F15" s="19" t="s">
         <v>155</v>
       </c>
-      <c r="F15" s="19" t="s">
-        <v>157</v>
-      </c>
       <c r="G15" s="19" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H15" s="19" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="I15" s="33"/>
     </row>
